--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -635,7 +635,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -663,7 +663,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -691,7 +691,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -719,7 +719,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -747,7 +747,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -775,7 +775,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -803,7 +803,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -831,7 +831,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -859,7 +859,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -887,7 +887,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -915,7 +915,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -943,7 +943,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -971,7 +971,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -999,7 +999,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
@@ -1027,7 +1027,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1055,7 +1055,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>961</v>
+        <v>1208</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1802</v>
+        <v>1558</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1125</v>
+        <v>1200</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1364</v>
+        <v>1290</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>683</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1548</v>
+        <v>963</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1214</v>
+        <v>1803</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1271</v>
+        <v>1125</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1218</v>
+        <v>1365</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>230</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1704</v>
+        <v>1548</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1058</v>
+        <v>1217</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1304</v>
+        <v>1271</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1183</v>
+        <v>1219</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>213</v>
+        <v>113</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1748</v>
+        <v>1704</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1014</v>
+        <v>1061</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>987</v>
+        <v>1015</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>326</v>
+        <v>218</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>86</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1623</v>
+        <v>1776</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1139</v>
+        <v>989</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1223</v>
+        <v>1300</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1261</v>
+        <v>1187</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>123</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1578</v>
+        <v>1624</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1184</v>
+        <v>1141</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1205</v>
+        <v>1224</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1279</v>
+        <v>1261</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1487</v>
+        <v>1579</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1274</v>
+        <v>1186</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1184</v>
+        <v>1205</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1298</v>
+        <v>1280</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>175</v>
+        <v>288</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>287</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1674</v>
+        <v>1488</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1087</v>
+        <v>1276</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1200</v>
+        <v>1185</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1280</v>
+        <v>1298</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1839</v>
+        <v>1674</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>921</v>
+        <v>1090</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1247</v>
+        <v>1199</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1231</v>
+        <v>1282</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>142</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1822</v>
+        <v>1838</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1222</v>
+        <v>1247</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1256</v>
+        <v>1232</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>136</v>
+        <v>206</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>280</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1989</v>
+        <v>1823</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>770</v>
+        <v>940</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1274</v>
+        <v>1222</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1204</v>
+        <v>1257</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>349</v>
+        <v>140</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>84</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1899</v>
+        <v>1988</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>857</v>
+        <v>774</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1215</v>
+        <v>1273</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1262</v>
+        <v>1206</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>276</v>
+        <v>349</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>121</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1927</v>
+        <v>1898</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>828</v>
+        <v>861</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1198</v>
+        <v>1215</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1278</v>
+        <v>1263</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>277</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>89</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1846</v>
+        <v>1926</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>909</v>
+        <v>832</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1171</v>
+        <v>1198</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1300</v>
+        <v>1279</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1832</v>
+        <v>1846</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1152</v>
+        <v>1172</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1319</v>
+        <v>1300</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1743</v>
+        <v>1832</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1012</v>
+        <v>925</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1122</v>
+        <v>1153</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1349</v>
+        <v>1319</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>584</v>
+        <v>265</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1313</v>
+        <v>1743</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1442</v>
+        <v>1014</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1020</v>
+        <v>1123</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1451</v>
+        <v>1349</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>832</v>
+        <v>584</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>767</v>
+        <v>1313</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1987</v>
+        <v>1444</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>892</v>
+        <v>1021</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1576</v>
+        <v>1451</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>110</v>
+        <v>831</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>336</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>936</v>
+        <v>768</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1818</v>
+        <v>1988</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>967</v>
+        <v>893</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1500</v>
+        <v>1576</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>387</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1208</v>
+        <v>1474</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1558</v>
+        <v>1290</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1200</v>
+        <v>1262</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1290</v>
+        <v>1232</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>421</v>
+        <v>321</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>963</v>
+        <v>1207</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1803</v>
+        <v>1556</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1125</v>
+        <v>1201</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1365</v>
+        <v>1290</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>685</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1548</v>
+        <v>961</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1217</v>
+        <v>1802</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1271</v>
+        <v>1126</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1219</v>
+        <v>1365</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>230</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1704</v>
+        <v>1546</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1061</v>
+        <v>1216</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1303</v>
+        <v>1272</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1185</v>
+        <v>1219</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>213</v>
+        <v>113</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>170</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1015</v>
+        <v>1062</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1776</v>
+        <v>1747</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>989</v>
+        <v>1015</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>327</v>
+        <v>217</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1624</v>
+        <v>1773</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1141</v>
+        <v>989</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1224</v>
+        <v>1300</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1261</v>
+        <v>1188</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>262</v>
+        <v>326</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>124</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1579</v>
+        <v>1621</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1186</v>
+        <v>1141</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1205</v>
+        <v>1224</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1280</v>
+        <v>1262</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1488</v>
+        <v>1578</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1276</v>
+        <v>1184</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1185</v>
+        <v>1205</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1298</v>
+        <v>1281</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>288</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1674</v>
+        <v>1486</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1090</v>
+        <v>1275</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1199</v>
+        <v>1186</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1282</v>
+        <v>1298</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1838</v>
+        <v>1671</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>925</v>
+        <v>1090</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1247</v>
+        <v>1200</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1232</v>
+        <v>1282</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>143</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1823</v>
+        <v>1837</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1222</v>
+        <v>1248</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1257</v>
+        <v>1232</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>279</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1988</v>
+        <v>1823</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>774</v>
+        <v>938</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1273</v>
+        <v>1223</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1206</v>
+        <v>1257</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>349</v>
+        <v>139</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>84</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1898</v>
+        <v>1988</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>861</v>
+        <v>772</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1215</v>
+        <v>1274</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1263</v>
+        <v>1206</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>277</v>
+        <v>348</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>121</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1926</v>
+        <v>1899</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>832</v>
+        <v>858</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1198</v>
+        <v>1216</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1279</v>
+        <v>1263</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1846</v>
+        <v>1926</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>912</v>
+        <v>830</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1172</v>
+        <v>1198</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1300</v>
+        <v>1280</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1832</v>
+        <v>1846</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>925</v>
+        <v>910</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1153</v>
+        <v>1172</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1319</v>
+        <v>1301</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1743</v>
+        <v>1832</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1014</v>
+        <v>923</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1123</v>
+        <v>1153</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1349</v>
+        <v>1320</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>584</v>
+        <v>265</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1313</v>
+        <v>1743</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1444</v>
+        <v>1012</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1021</v>
+        <v>1123</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1451</v>
+        <v>1350</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>831</v>
+        <v>584</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>768</v>
+        <v>1314</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1988</v>
+        <v>1441</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>893</v>
+        <v>1021</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1576</v>
+        <v>1452</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>110</v>
+        <v>830</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>338</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1474</v>
+        <v>1526</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1290</v>
+        <v>1270</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1262</v>
+        <v>1309</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1232</v>
+        <v>1211</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>59</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1207</v>
+        <v>1489</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1556</v>
+        <v>1303</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1201</v>
+        <v>1275</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1290</v>
+        <v>1243</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>421</v>
+        <v>326</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>961</v>
+        <v>1219</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1802</v>
+        <v>1572</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1126</v>
+        <v>1214</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1365</v>
+        <v>1301</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>685</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1546</v>
+        <v>975</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1216</v>
+        <v>1816</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1272</v>
+        <v>1138</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1219</v>
+        <v>1377</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>229</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1700</v>
+        <v>1564</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1062</v>
+        <v>1226</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1303</v>
+        <v>1285</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1186</v>
+        <v>1230</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1747</v>
+        <v>1719</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1015</v>
+        <v>1071</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1301</v>
+        <v>1317</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>127</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1773</v>
+        <v>1767</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>989</v>
+        <v>1023</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1300</v>
+        <v>1314</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1188</v>
+        <v>1199</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>326</v>
+        <v>230</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1621</v>
+        <v>1789</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1141</v>
+        <v>1001</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1224</v>
+        <v>1309</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1262</v>
+        <v>1203</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>261</v>
+        <v>336</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1578</v>
+        <v>1630</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1184</v>
+        <v>1160</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1205</v>
+        <v>1231</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1486</v>
+        <v>1589</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1275</v>
+        <v>1201</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1186</v>
+        <v>1212</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>1298</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>175</v>
+        <v>296</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>287</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1671</v>
+        <v>1499</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1090</v>
+        <v>1290</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1282</v>
+        <v>1314</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1837</v>
+        <v>1682</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>924</v>
+        <v>1106</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1248</v>
+        <v>1207</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1232</v>
+        <v>1299</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>144</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1823</v>
+        <v>1846</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1223</v>
+        <v>1256</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1257</v>
+        <v>1248</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>279</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1988</v>
+        <v>1831</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>772</v>
+        <v>957</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1274</v>
+        <v>1231</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1206</v>
+        <v>1273</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>348</v>
+        <v>146</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>83</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1899</v>
+        <v>1996</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>858</v>
+        <v>791</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1216</v>
+        <v>1282</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1263</v>
+        <v>1222</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>278</v>
+        <v>352</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1926</v>
+        <v>1910</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>830</v>
+        <v>874</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1198</v>
+        <v>1224</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1846</v>
+        <v>1939</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>910</v>
+        <v>844</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1172</v>
+        <v>1208</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1301</v>
+        <v>1294</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1832</v>
+        <v>1857</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1743</v>
+        <v>1842</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1012</v>
+        <v>940</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1123</v>
+        <v>1161</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1350</v>
+        <v>1336</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>584</v>
+        <v>270</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1314</v>
+        <v>1754</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1441</v>
+        <v>1028</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1021</v>
+        <v>1132</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1452</v>
+        <v>1365</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>830</v>
+        <v>592</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1526</v>
+        <v>1221</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1270</v>
+        <v>1556</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1309</v>
+        <v>1226</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1211</v>
+        <v>1277</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>287</v>
+        <v>108</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>106</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1489</v>
+        <v>1519</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1303</v>
+        <v>1258</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1275</v>
+        <v>1305</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1243</v>
+        <v>1198</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1219</v>
+        <v>1486</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1572</v>
+        <v>1287</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1214</v>
+        <v>1271</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1301</v>
+        <v>1230</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>426</v>
+        <v>324</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>975</v>
+        <v>1214</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1816</v>
+        <v>1558</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1138</v>
+        <v>1209</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1377</v>
+        <v>1289</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>83</v>
+        <v>424</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>697</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1564</v>
+        <v>966</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1226</v>
+        <v>1806</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1285</v>
+        <v>1133</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1230</v>
+        <v>1365</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>240</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1719</v>
+        <v>1556</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1071</v>
+        <v>1215</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1317</v>
+        <v>1281</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1196</v>
+        <v>1217</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>178</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1767</v>
+        <v>1711</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1023</v>
+        <v>1060</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1199</v>
+        <v>1184</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>127</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1789</v>
+        <v>1759</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>1309</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1203</v>
+        <v>1187</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>336</v>
+        <v>222</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1630</v>
+        <v>1782</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1160</v>
+        <v>989</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1231</v>
+        <v>1305</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1279</v>
+        <v>1190</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>130</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1589</v>
+        <v>1626</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1201</v>
+        <v>1145</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1212</v>
+        <v>1227</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1298</v>
+        <v>1266</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1499</v>
+        <v>1584</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1290</v>
+        <v>1187</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1194</v>
+        <v>1209</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1314</v>
+        <v>1284</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>183</v>
+        <v>287</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>292</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1682</v>
+        <v>1494</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1106</v>
+        <v>1276</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1207</v>
+        <v>1190</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1846</v>
+        <v>1675</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>942</v>
+        <v>1094</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1256</v>
+        <v>1203</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1248</v>
+        <v>1286</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>214</v>
+        <v>131</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>150</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>957</v>
+        <v>929</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1231</v>
+        <v>1252</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1273</v>
+        <v>1235</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>285</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1996</v>
+        <v>1826</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>791</v>
+        <v>943</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1282</v>
+        <v>1227</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1222</v>
+        <v>1260</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>352</v>
+        <v>139</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>92</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1910</v>
+        <v>1991</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>874</v>
+        <v>777</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1224</v>
+        <v>1278</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1279</v>
+        <v>1209</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>280</v>
+        <v>347</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>134</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1939</v>
+        <v>1903</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>844</v>
+        <v>862</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1208</v>
+        <v>1219</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1294</v>
+        <v>1267</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1857</v>
+        <v>1931</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>926</v>
+        <v>833</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1180</v>
+        <v>1203</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1317</v>
+        <v>1282</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1842</v>
+        <v>1850</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>940</v>
+        <v>914</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1161</v>
+        <v>1176</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1336</v>
+        <v>1304</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1754</v>
+        <v>1835</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1028</v>
+        <v>928</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1132</v>
+        <v>1157</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1365</v>
+        <v>1323</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>592</v>
+        <v>264</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1221</v>
+        <v>1298</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1556</v>
+        <v>1482</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1226</v>
+        <v>1251</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1277</v>
+        <v>1255</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>223</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1519</v>
+        <v>1222</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1258</v>
+        <v>1558</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1305</v>
+        <v>1228</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1198</v>
+        <v>1278</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>98</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1486</v>
+        <v>1520</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1287</v>
+        <v>1260</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1271</v>
+        <v>1307</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1230</v>
+        <v>1199</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>324</v>
+        <v>282</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1214</v>
+        <v>1487</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1558</v>
+        <v>1289</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1209</v>
+        <v>1273</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1289</v>
+        <v>1231</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>424</v>
+        <v>324</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>966</v>
+        <v>1216</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1806</v>
+        <v>1559</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1133</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1365</v>
+        <v>1290</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>80</v>
+        <v>423</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>689</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1556</v>
+        <v>967</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1215</v>
+        <v>1808</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1281</v>
+        <v>1135</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1217</v>
+        <v>1366</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>233</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1711</v>
+        <v>1556</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1060</v>
+        <v>1218</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1312</v>
+        <v>1283</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1184</v>
+        <v>1218</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>173</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1759</v>
+        <v>1712</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1012</v>
+        <v>1062</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>127</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1782</v>
+        <v>1760</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>989</v>
+        <v>1014</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>329</v>
+        <v>221</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1626</v>
+        <v>1784</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1145</v>
+        <v>990</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1227</v>
+        <v>1307</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1266</v>
+        <v>1191</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>262</v>
+        <v>329</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>126</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1584</v>
+        <v>1629</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1187</v>
+        <v>1145</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1209</v>
+        <v>1229</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1284</v>
+        <v>1267</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1494</v>
+        <v>1585</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1276</v>
+        <v>1189</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1190</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1301</v>
+        <v>1285</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>175</v>
+        <v>286</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>288</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1675</v>
+        <v>1497</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1094</v>
+        <v>1276</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1203</v>
+        <v>1192</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1286</v>
+        <v>1302</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1840</v>
+        <v>1678</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>929</v>
+        <v>1094</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1252</v>
+        <v>1205</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1235</v>
+        <v>1287</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>145</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1826</v>
+        <v>1843</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>943</v>
+        <v>929</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1227</v>
+        <v>1254</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1260</v>
+        <v>1236</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>280</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1991</v>
+        <v>1827</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>777</v>
+        <v>945</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1278</v>
+        <v>1229</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1209</v>
+        <v>1261</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>347</v>
+        <v>139</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>84</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1903</v>
+        <v>1993</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>862</v>
+        <v>778</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1219</v>
+        <v>1280</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1267</v>
+        <v>1210</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>279</v>
+        <v>347</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>123</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1931</v>
+        <v>1905</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>833</v>
+        <v>863</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1203</v>
+        <v>1221</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1282</v>
+        <v>1268</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1850</v>
+        <v>1933</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>914</v>
+        <v>834</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1176</v>
+        <v>1205</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1304</v>
+        <v>1283</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1835</v>
+        <v>1853</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1157</v>
+        <v>1178</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1323</v>
+        <v>1305</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1298</v>
+        <v>1236</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1482</v>
+        <v>1548</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1251</v>
+        <v>1238</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1255</v>
+        <v>1269</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1222</v>
+        <v>1299</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1558</v>
+        <v>1483</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1228</v>
+        <v>1251</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1278</v>
+        <v>1255</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>223</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1520</v>
+        <v>1223</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1260</v>
+        <v>1559</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1307</v>
+        <v>1228</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1199</v>
+        <v>1278</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>99</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1487</v>
+        <v>1521</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1289</v>
+        <v>1261</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1273</v>
+        <v>1307</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1231</v>
+        <v>1199</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1216</v>
+        <v>1488</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1559</v>
+        <v>1290</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1211</v>
+        <v>1273</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1290</v>
+        <v>1231</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>423</v>
+        <v>325</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>967</v>
+        <v>1217</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1808</v>
+        <v>1560</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1135</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1366</v>
+        <v>1290</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>80</v>
+        <v>423</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>688</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1556</v>
+        <v>969</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1218</v>
+        <v>1808</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1283</v>
+        <v>1135</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1218</v>
+        <v>1366</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>233</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1712</v>
+        <v>1556</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1062</v>
+        <v>1220</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1314</v>
+        <v>1283</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1185</v>
+        <v>1218</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>213</v>
+        <v>114</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>172</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1760</v>
+        <v>1713</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1014</v>
+        <v>1063</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>127</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1784</v>
+        <v>1760</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>990</v>
+        <v>1016</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>329</v>
+        <v>221</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>86</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1629</v>
+        <v>1784</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1145</v>
+        <v>992</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1229</v>
+        <v>1307</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1267</v>
+        <v>1191</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>263</v>
+        <v>329</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>124</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1585</v>
+        <v>1630</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1189</v>
+        <v>1146</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1211</v>
+        <v>1229</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1285</v>
+        <v>1267</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1497</v>
+        <v>1586</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1276</v>
+        <v>1190</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1192</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1302</v>
+        <v>1285</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>175</v>
+        <v>286</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>287</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1678</v>
+        <v>1498</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1094</v>
+        <v>1277</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1205</v>
+        <v>1192</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1287</v>
+        <v>1302</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1843</v>
+        <v>1679</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>929</v>
+        <v>1095</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1254</v>
+        <v>1205</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1236</v>
+        <v>1287</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>146</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1827</v>
+        <v>1844</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1229</v>
+        <v>1254</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1261</v>
+        <v>1236</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>280</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1993</v>
+        <v>1827</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>778</v>
+        <v>947</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1280</v>
+        <v>1229</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1210</v>
+        <v>1261</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>347</v>
+        <v>139</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>84</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1905</v>
+        <v>1994</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>863</v>
+        <v>779</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1221</v>
+        <v>1280</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1268</v>
+        <v>1210</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>280</v>
+        <v>347</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1933</v>
+        <v>1905</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>834</v>
+        <v>865</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1205</v>
+        <v>1221</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1283</v>
+        <v>1268</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1853</v>
+        <v>1933</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>914</v>
+        <v>836</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1178</v>
+        <v>1205</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1305</v>
+        <v>1283</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,166 +523,166 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1236</v>
+        <v>1181</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1548</v>
+        <v>1597</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1269</v>
+        <v>1276</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>121</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1299</v>
+        <v>1233</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1483</v>
+        <v>1545</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1251</v>
+        <v>1235</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1255</v>
+        <v>1269</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1223</v>
+        <v>1294</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1559</v>
+        <v>1482</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1228</v>
+        <v>1248</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1278</v>
+        <v>1255</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>222</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1521</v>
+        <v>1219</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1261</v>
+        <v>1557</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1307</v>
+        <v>1225</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1199</v>
+        <v>1278</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>98</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1488</v>
+        <v>1517</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1290</v>
+        <v>1259</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1273</v>
+        <v>1304</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1231</v>
+        <v>1199</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1217</v>
+        <v>1483</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1560</v>
+        <v>1289</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1211</v>
+        <v>1270</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1290</v>
+        <v>1231</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>423</v>
+        <v>325</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>56</v>
@@ -691,393 +691,393 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>969</v>
+        <v>1211</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1808</v>
+        <v>1560</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1135</v>
+        <v>1208</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1366</v>
+        <v>1290</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>688</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1556</v>
+        <v>963</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1220</v>
+        <v>1808</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1283</v>
+        <v>1132</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1218</v>
+        <v>1366</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>234</v>
+        <v>688</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1713</v>
+        <v>1551</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1063</v>
+        <v>1219</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1314</v>
+        <v>1280</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1185</v>
+        <v>1218</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>214</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>172</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1760</v>
+        <v>1708</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1016</v>
+        <v>1062</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>1311</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>128</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1784</v>
+        <v>1755</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>992</v>
+        <v>1015</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>329</v>
+        <v>220</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>88</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1630</v>
+        <v>1779</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1146</v>
+        <v>991</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1229</v>
+        <v>1304</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1267</v>
+        <v>1191</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>124</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1586</v>
+        <v>1625</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1190</v>
+        <v>1145</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1211</v>
+        <v>1226</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1285</v>
+        <v>1267</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1498</v>
+        <v>1580</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1277</v>
+        <v>1190</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1192</v>
+        <v>1208</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1302</v>
+        <v>1285</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>175</v>
+        <v>286</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>286</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1679</v>
+        <v>1492</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1095</v>
+        <v>1277</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1205</v>
+        <v>1189</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1287</v>
+        <v>1302</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1844</v>
+        <v>1673</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>930</v>
+        <v>1095</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1254</v>
+        <v>1202</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1236</v>
+        <v>1287</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>145</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1827</v>
+        <v>1840</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>947</v>
+        <v>928</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1229</v>
+        <v>1251</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1261</v>
+        <v>1236</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>279</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1994</v>
+        <v>1822</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>779</v>
+        <v>946</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1280</v>
+        <v>1226</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1210</v>
+        <v>1261</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>347</v>
+        <v>136</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>84</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1905</v>
+        <v>1990</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>865</v>
+        <v>777</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1221</v>
+        <v>1277</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1268</v>
+        <v>1210</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1933</v>
+        <v>1901</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1283</v>
+        <v>1268</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>91</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1181</v>
+        <v>1284</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1597</v>
+        <v>1505</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1230</v>
+        <v>1262</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1276</v>
+        <v>1257</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>217</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1233</v>
+        <v>1184</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1545</v>
+        <v>1605</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1269</v>
+        <v>1287</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1294</v>
+        <v>1233</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1482</v>
+        <v>1556</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1248</v>
+        <v>1235</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1255</v>
+        <v>1281</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1219</v>
+        <v>1297</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1557</v>
+        <v>1490</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1278</v>
+        <v>1265</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>222</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1517</v>
+        <v>1224</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1259</v>
+        <v>1563</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1304</v>
+        <v>1226</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1199</v>
+        <v>1289</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>279</v>
+        <v>110</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>98</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1483</v>
+        <v>1523</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1289</v>
+        <v>1264</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1270</v>
+        <v>1304</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1231</v>
+        <v>1211</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>325</v>
+        <v>281</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>56</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1211</v>
+        <v>1487</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1560</v>
+        <v>1296</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1208</v>
+        <v>1271</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1290</v>
+        <v>1242</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>422</v>
+        <v>331</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>963</v>
+        <v>1216</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1808</v>
+        <v>1566</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1132</v>
+        <v>1209</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1366</v>
+        <v>1301</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>688</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1551</v>
+        <v>968</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1219</v>
+        <v>1814</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1280</v>
+        <v>1132</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1218</v>
+        <v>1378</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>233</v>
+        <v>689</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1708</v>
+        <v>1552</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1062</v>
+        <v>1229</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1311</v>
+        <v>1280</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1185</v>
+        <v>1230</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>213</v>
+        <v>121</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>171</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1755</v>
+        <v>1710</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1015</v>
+        <v>1071</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>128</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1779</v>
+        <v>1759</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>991</v>
+        <v>1022</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>328</v>
+        <v>228</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1625</v>
+        <v>1782</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1145</v>
+        <v>999</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1226</v>
+        <v>1305</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1267</v>
+        <v>1202</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>122</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1580</v>
+        <v>1628</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1190</v>
+        <v>1153</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1492</v>
+        <v>1581</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1277</v>
+        <v>1200</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1189</v>
+        <v>1209</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>174</v>
+        <v>292</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>285</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1673</v>
+        <v>1492</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1095</v>
+        <v>1288</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1202</v>
+        <v>1189</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1287</v>
+        <v>1314</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1840</v>
+        <v>1676</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>928</v>
+        <v>1103</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1251</v>
+        <v>1202</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1236</v>
+        <v>1299</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>144</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1822</v>
+        <v>1843</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1226</v>
+        <v>1251</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1261</v>
+        <v>1248</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>279</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1990</v>
+        <v>1826</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>777</v>
+        <v>953</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1277</v>
+        <v>1225</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1210</v>
+        <v>1274</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>346</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>84</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1901</v>
+        <v>1992</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>863</v>
+        <v>786</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1218</v>
+        <v>1276</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1268</v>
+        <v>1223</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>279</v>
+        <v>350</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,222 +523,222 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1284</v>
+        <v>1381</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1505</v>
+        <v>1396</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1262</v>
+        <v>1290</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1257</v>
+        <v>1220</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>123</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1184</v>
+        <v>1280</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1605</v>
+        <v>1497</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1231</v>
+        <v>1260</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1287</v>
+        <v>1247</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>224</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1233</v>
+        <v>1182</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1556</v>
+        <v>1595</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>126</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1297</v>
+        <v>1231</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1490</v>
+        <v>1546</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1250</v>
+        <v>1234</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>200</v>
+        <v>142</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1224</v>
+        <v>1293</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1563</v>
+        <v>1482</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1226</v>
+        <v>1249</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1289</v>
+        <v>1254</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>228</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1523</v>
+        <v>1218</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1264</v>
+        <v>1557</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1304</v>
+        <v>1225</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1211</v>
+        <v>1278</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>281</v>
+        <v>106</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>104</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1487</v>
+        <v>1519</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1296</v>
+        <v>1256</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1271</v>
+        <v>1304</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1242</v>
+        <v>1199</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1216</v>
+        <v>1482</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1566</v>
+        <v>1289</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1209</v>
+        <v>1270</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1301</v>
+        <v>1231</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>430</v>
+        <v>324</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>56</v>
@@ -747,337 +747,337 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>968</v>
+        <v>1210</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1814</v>
+        <v>1560</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1132</v>
+        <v>1208</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1378</v>
+        <v>1290</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>89</v>
+        <v>421</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>689</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1552</v>
+        <v>962</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1229</v>
+        <v>1808</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1280</v>
+        <v>1132</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1230</v>
+        <v>1366</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>237</v>
+        <v>688</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1710</v>
+        <v>1549</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1071</v>
+        <v>1220</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1312</v>
+        <v>1279</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1196</v>
+        <v>1219</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1759</v>
+        <v>1706</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1022</v>
+        <v>1063</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>130</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1782</v>
+        <v>1755</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>999</v>
+        <v>1014</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1202</v>
+        <v>1188</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>332</v>
+        <v>219</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>94</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1628</v>
+        <v>1778</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1153</v>
+        <v>991</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1227</v>
+        <v>1304</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1278</v>
+        <v>1191</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1581</v>
+        <v>1626</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1200</v>
+        <v>1143</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1209</v>
+        <v>1226</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1296</v>
+        <v>1267</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>292</v>
+        <v>263</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1492</v>
+        <v>1581</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1288</v>
+        <v>1188</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1189</v>
+        <v>1209</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1314</v>
+        <v>1284</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>178</v>
+        <v>285</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>293</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1676</v>
+        <v>1490</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1103</v>
+        <v>1278</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1202</v>
+        <v>1189</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1843</v>
+        <v>1674</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>936</v>
+        <v>1093</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1251</v>
+        <v>1202</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1248</v>
+        <v>1287</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>150</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1826</v>
+        <v>1838</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1225</v>
+        <v>1251</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1274</v>
+        <v>1236</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>282</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1992</v>
+        <v>1822</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>786</v>
+        <v>945</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1276</v>
+        <v>1226</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1223</v>
+        <v>1261</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>350</v>
+        <v>136</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>89</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,250 +523,250 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1381</v>
+        <v>1078</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1396</v>
+        <v>1698</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1290</v>
+        <v>1209</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1220</v>
+        <v>1301</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>205</v>
+        <v>126</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>90</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1280</v>
+        <v>1379</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1497</v>
+        <v>1396</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1260</v>
+        <v>1290</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1247</v>
+        <v>1218</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1182</v>
+        <v>1279</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1595</v>
+        <v>1496</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1231</v>
+        <v>1260</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1275</v>
+        <v>1245</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>101</v>
+        <v>210</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>215</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>1231</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>1546</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1234</v>
-      </c>
       <c r="F5" s="5" t="n">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>119</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1293</v>
+        <v>1229</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1482</v>
+        <v>1546</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1249</v>
+        <v>1234</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1254</v>
+        <v>1268</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1218</v>
+        <v>1292</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1557</v>
+        <v>1481</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1278</v>
+        <v>1252</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>222</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1519</v>
+        <v>1217</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1256</v>
+        <v>1556</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1304</v>
+        <v>1225</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1199</v>
+        <v>1276</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>280</v>
+        <v>106</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>97</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1482</v>
+        <v>1518</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1289</v>
+        <v>1255</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1270</v>
+        <v>1304</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1231</v>
+        <v>1197</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>324</v>
+        <v>279</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>56</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1210</v>
+        <v>1481</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1560</v>
+        <v>1288</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1208</v>
+        <v>1270</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1290</v>
+        <v>1229</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>421</v>
+        <v>324</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>55</v>
@@ -775,250 +775,250 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>962</v>
+        <v>1210</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1808</v>
+        <v>1558</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1132</v>
+        <v>1208</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1366</v>
+        <v>1288</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>688</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1549</v>
+        <v>961</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1220</v>
+        <v>1807</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1279</v>
+        <v>1132</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1219</v>
+        <v>1364</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>232</v>
+        <v>688</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1706</v>
+        <v>1549</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1063</v>
+        <v>1218</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1311</v>
+        <v>1279</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1185</v>
+        <v>1217</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>210</v>
+        <v>116</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>171</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1755</v>
+        <v>1705</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1014</v>
+        <v>1062</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>128</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1778</v>
+        <v>1755</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>991</v>
+        <v>1012</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>327</v>
+        <v>219</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>89</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1626</v>
+        <v>1777</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1143</v>
+        <v>990</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1226</v>
+        <v>1304</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1267</v>
+        <v>1189</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>121</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1581</v>
+        <v>1625</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1188</v>
+        <v>1142</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1209</v>
+        <v>1226</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1284</v>
+        <v>1265</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1490</v>
+        <v>1579</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1278</v>
+        <v>1188</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1189</v>
+        <v>1209</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1302</v>
+        <v>1282</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>174</v>
+        <v>286</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>287</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1674</v>
+        <v>1488</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1093</v>
+        <v>1278</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1202</v>
+        <v>1189</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1287</v>
+        <v>1300</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>286</v>
@@ -1027,57 +1027,57 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1838</v>
+        <v>1672</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>929</v>
+        <v>1093</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1251</v>
+        <v>1202</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1236</v>
+        <v>1285</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>144</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1822</v>
+        <v>1835</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1226</v>
+        <v>1251</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1261</v>
+        <v>1234</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>136</v>
+        <v>206</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>278</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1078</v>
+        <v>870</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1698</v>
+        <v>1902</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1209</v>
+        <v>1175</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1301</v>
+        <v>1334</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>271</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1379</v>
+        <v>1077</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1396</v>
+        <v>1695</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1290</v>
+        <v>1207</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1218</v>
+        <v>1298</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>91</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1279</v>
+        <v>1379</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1496</v>
+        <v>1392</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1260</v>
+        <v>1288</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1245</v>
+        <v>1215</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1180</v>
+        <v>1279</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1595</v>
+        <v>1492</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1231</v>
+        <v>1258</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1273</v>
+        <v>1242</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>215</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1591</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>1229</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>1546</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1234</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>118</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1292</v>
+        <v>1229</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1481</v>
+        <v>1542</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1249</v>
+        <v>1231</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1252</v>
+        <v>1266</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>198</v>
+        <v>141</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1217</v>
+        <v>1292</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1556</v>
+        <v>1477</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1225</v>
+        <v>1246</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1276</v>
+        <v>1250</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>222</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1518</v>
+        <v>1217</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1255</v>
+        <v>1552</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1304</v>
+        <v>1222</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1197</v>
+        <v>1274</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>279</v>
+        <v>106</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>97</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1481</v>
+        <v>1518</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1288</v>
+        <v>1251</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1270</v>
+        <v>1301</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1229</v>
+        <v>1195</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1210</v>
+        <v>1480</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1558</v>
+        <v>1285</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1208</v>
+        <v>1268</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1288</v>
+        <v>1226</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>421</v>
+        <v>323</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>961</v>
+        <v>1210</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1807</v>
+        <v>1554</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1132</v>
+        <v>1205</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1364</v>
+        <v>1286</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>688</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1549</v>
+        <v>960</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1218</v>
+        <v>1804</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1279</v>
+        <v>1129</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1217</v>
+        <v>1362</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>232</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1705</v>
+        <v>1549</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1062</v>
+        <v>1214</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1311</v>
+        <v>1275</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1183</v>
+        <v>1216</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>171</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1755</v>
+        <v>1703</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1012</v>
+        <v>1060</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>127</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1777</v>
+        <v>1753</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>990</v>
+        <v>1010</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1304</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>327</v>
+        <v>217</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>89</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1625</v>
+        <v>1776</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1142</v>
+        <v>987</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1226</v>
+        <v>1300</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1265</v>
+        <v>1188</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1579</v>
+        <v>1624</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1188</v>
+        <v>1139</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1282</v>
+        <v>1264</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1488</v>
+        <v>1578</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1278</v>
+        <v>1185</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1189</v>
+        <v>1205</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1300</v>
+        <v>1281</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>174</v>
+        <v>286</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>286</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1672</v>
+        <v>1487</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1093</v>
+        <v>1275</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1202</v>
+        <v>1185</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1285</v>
+        <v>1299</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1835</v>
+        <v>1669</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>930</v>
+        <v>1092</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1251</v>
+        <v>1197</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1234</v>
+        <v>1285</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>144</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1902</v>
+        <v>1911</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1175</v>
+        <v>1164</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1334</v>
+        <v>1354</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1077</v>
+        <v>871</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1695</v>
+        <v>1907</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1207</v>
+        <v>1176</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1298</v>
+        <v>1338</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>271</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1379</v>
+        <v>1080</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1392</v>
+        <v>1698</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1288</v>
+        <v>1208</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1215</v>
+        <v>1302</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>91</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1279</v>
+        <v>1382</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1492</v>
+        <v>1395</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1258</v>
+        <v>1289</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1242</v>
+        <v>1219</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1180</v>
+        <v>1281</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1591</v>
+        <v>1496</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1229</v>
+        <v>1259</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1270</v>
+        <v>1246</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>99</v>
+        <v>209</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1229</v>
+        <v>1182</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1542</v>
+        <v>1595</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>1231</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1266</v>
+        <v>1273</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>117</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1292</v>
+        <v>1232</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1477</v>
+        <v>1545</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1250</v>
+        <v>1269</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1217</v>
+        <v>1295</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1552</v>
+        <v>1480</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1222</v>
+        <v>1248</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1274</v>
+        <v>1253</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>221</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1518</v>
+        <v>1219</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1251</v>
+        <v>1556</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1301</v>
+        <v>1224</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1195</v>
+        <v>1277</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>278</v>
+        <v>107</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>96</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1480</v>
+        <v>1520</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1285</v>
+        <v>1255</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1268</v>
+        <v>1302</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1226</v>
+        <v>1199</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>323</v>
+        <v>278</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>53</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1210</v>
+        <v>1482</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1554</v>
+        <v>1289</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1205</v>
+        <v>1270</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1286</v>
+        <v>1229</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>960</v>
+        <v>1212</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1804</v>
+        <v>1558</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1129</v>
+        <v>1207</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1362</v>
+        <v>1289</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>687</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1549</v>
+        <v>961</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1214</v>
+        <v>1809</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1275</v>
+        <v>1132</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1216</v>
+        <v>1364</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>229</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1703</v>
+        <v>1552</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1060</v>
+        <v>1217</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1307</v>
+        <v>1278</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1182</v>
+        <v>1218</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>171</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1753</v>
+        <v>1707</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1010</v>
+        <v>1062</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>125</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1776</v>
+        <v>1756</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>987</v>
+        <v>1013</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1300</v>
+        <v>1307</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>327</v>
+        <v>217</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1624</v>
+        <v>1779</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1139</v>
+        <v>990</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1222</v>
+        <v>1303</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1264</v>
+        <v>1190</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1578</v>
+        <v>1627</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1185</v>
+        <v>1142</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1205</v>
+        <v>1225</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1281</v>
+        <v>1266</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1487</v>
+        <v>1582</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1275</v>
+        <v>1187</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1185</v>
+        <v>1208</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>174</v>
+        <v>285</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>283</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1669</v>
+        <v>1493</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1092</v>
+        <v>1275</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1197</v>
+        <v>1189</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1285</v>
+        <v>1300</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>868</v>
+        <v>1144</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1911</v>
+        <v>1651</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1164</v>
+        <v>1233</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1354</v>
+        <v>1305</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>182</v>
+        <v>344</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1907</v>
+        <v>1921</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1338</v>
+        <v>1366</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>198</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1080</v>
+        <v>876</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1698</v>
+        <v>1918</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1208</v>
+        <v>1181</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1302</v>
+        <v>1351</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>272</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1382</v>
+        <v>1084</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1395</v>
+        <v>1710</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1289</v>
+        <v>1213</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1219</v>
+        <v>1315</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>91</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1281</v>
+        <v>1388</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1496</v>
+        <v>1405</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1259</v>
+        <v>1295</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1246</v>
+        <v>1231</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1182</v>
+        <v>1289</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1595</v>
+        <v>1504</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1231</v>
+        <v>1265</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1273</v>
+        <v>1258</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>215</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1232</v>
+        <v>1189</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1545</v>
+        <v>1604</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1269</v>
+        <v>1286</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>118</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1295</v>
+        <v>1240</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1480</v>
+        <v>1553</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1248</v>
+        <v>1239</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1253</v>
+        <v>1281</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1219</v>
+        <v>1304</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1556</v>
+        <v>1487</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1224</v>
+        <v>1254</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>107</v>
+        <v>206</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>221</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1520</v>
+        <v>1227</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1255</v>
+        <v>1564</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1302</v>
+        <v>1229</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1199</v>
+        <v>1290</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>278</v>
+        <v>116</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>99</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1482</v>
+        <v>1524</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1289</v>
+        <v>1267</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1270</v>
+        <v>1307</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1229</v>
+        <v>1212</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1212</v>
+        <v>1486</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1558</v>
+        <v>1301</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1207</v>
+        <v>1275</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1289</v>
+        <v>1242</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>420</v>
+        <v>332</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>961</v>
+        <v>1219</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1809</v>
+        <v>1567</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1132</v>
+        <v>1213</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1364</v>
+        <v>1301</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>689</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1552</v>
+        <v>967</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1217</v>
+        <v>1819</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1278</v>
+        <v>1137</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1218</v>
+        <v>1377</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>230</v>
+        <v>696</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1707</v>
+        <v>1557</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1062</v>
+        <v>1228</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1310</v>
+        <v>1283</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1184</v>
+        <v>1231</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>172</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1756</v>
+        <v>1711</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1013</v>
+        <v>1074</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1187</v>
+        <v>1197</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>127</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1779</v>
+        <v>1760</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>990</v>
+        <v>1025</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1303</v>
+        <v>1312</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1190</v>
+        <v>1200</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>327</v>
+        <v>222</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>88</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1627</v>
+        <v>1784</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1142</v>
+        <v>1001</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1225</v>
+        <v>1308</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1266</v>
+        <v>1203</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>263</v>
+        <v>328</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>123</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1582</v>
+        <v>1633</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1187</v>
+        <v>1152</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1208</v>
+        <v>1230</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1493</v>
+        <v>1588</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1275</v>
+        <v>1197</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1189</v>
+        <v>1212</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>175</v>
+        <v>291</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>284</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1144</v>
+        <v>962</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1651</v>
+        <v>1819</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1233</v>
+        <v>1179</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1305</v>
+        <v>1343</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>344</v>
+        <v>128</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>115</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>874</v>
+        <v>1138</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1921</v>
+        <v>1640</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1170</v>
+        <v>1229</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1366</v>
+        <v>1291</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>188</v>
+        <v>341</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1918</v>
+        <v>1911</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1181</v>
+        <v>1165</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>207</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1084</v>
+        <v>870</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1710</v>
+        <v>1907</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1213</v>
+        <v>1177</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1315</v>
+        <v>1337</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>280</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1388</v>
+        <v>1081</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1405</v>
+        <v>1696</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1295</v>
+        <v>1209</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1231</v>
+        <v>1301</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>100</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
+        <v>1381</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1395</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>1289</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>1504</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1265</v>
-      </c>
       <c r="F7" s="5" t="n">
-        <v>1258</v>
+        <v>1219</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>125</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1189</v>
+        <v>1281</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1604</v>
+        <v>1495</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1286</v>
+        <v>1245</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>221</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1240</v>
+        <v>1181</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1553</v>
+        <v>1595</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1281</v>
+        <v>1272</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1304</v>
+        <v>1231</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1487</v>
+        <v>1545</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1254</v>
+        <v>1234</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1227</v>
+        <v>1296</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1564</v>
+        <v>1478</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1229</v>
+        <v>1249</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1290</v>
+        <v>1252</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>116</v>
+        <v>196</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>222</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1524</v>
+        <v>1218</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1267</v>
+        <v>1556</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1307</v>
+        <v>1225</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1212</v>
+        <v>1276</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>285</v>
+        <v>106</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>105</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1486</v>
+        <v>1520</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1301</v>
+        <v>1254</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1275</v>
+        <v>1302</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1242</v>
+        <v>1199</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>332</v>
+        <v>277</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1219</v>
+        <v>1481</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1567</v>
+        <v>1289</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1213</v>
+        <v>1271</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1301</v>
+        <v>1228</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>429</v>
+        <v>325</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>967</v>
+        <v>1212</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1819</v>
+        <v>1557</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1137</v>
+        <v>1207</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1377</v>
+        <v>1289</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>87</v>
+        <v>420</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>696</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1557</v>
+        <v>961</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1228</v>
+        <v>1808</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1283</v>
+        <v>1132</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1231</v>
+        <v>1364</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>236</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1711</v>
+        <v>1552</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1074</v>
+        <v>1216</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1315</v>
+        <v>1278</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1197</v>
+        <v>1218</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>218</v>
+        <v>118</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>179</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1760</v>
+        <v>1707</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1025</v>
+        <v>1061</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1200</v>
+        <v>1184</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>135</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1784</v>
+        <v>1757</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1203</v>
+        <v>1187</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>328</v>
+        <v>217</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1633</v>
+        <v>1779</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1152</v>
+        <v>989</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1230</v>
+        <v>1303</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1279</v>
+        <v>1190</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>268</v>
+        <v>325</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>131</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1588</v>
+        <v>1626</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1197</v>
+        <v>1142</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1212</v>
+        <v>1226</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>962</v>
+        <v>1178</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1819</v>
+        <v>1602</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1179</v>
+        <v>1239</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1343</v>
+        <v>1283</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>128</v>
+        <v>272</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1138</v>
+        <v>962</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1640</v>
+        <v>1817</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1229</v>
+        <v>1178</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1291</v>
+        <v>1342</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>341</v>
+        <v>127</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>106</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>867</v>
+        <v>1138</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1911</v>
+        <v>1638</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1165</v>
+        <v>1228</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1353</v>
+        <v>1290</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>182</v>
+        <v>341</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1177</v>
+        <v>1164</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1337</v>
+        <v>1352</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1081</v>
+        <v>868</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1696</v>
+        <v>1907</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1209</v>
+        <v>1176</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1301</v>
+        <v>1336</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>270</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1381</v>
+        <v>1080</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1395</v>
+        <v>1695</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1289</v>
+        <v>1209</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1219</v>
+        <v>1299</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>204</v>
+        <v>128</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>93</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1281</v>
+        <v>1379</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1495</v>
+        <v>1395</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1260</v>
+        <v>1288</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1245</v>
+        <v>1218</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1181</v>
+        <v>1278</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1595</v>
+        <v>1496</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1232</v>
+        <v>1259</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1272</v>
+        <v>1244</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>213</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>1179</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>1231</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>1545</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1234</v>
-      </c>
       <c r="F10" s="3" t="n">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>120</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1296</v>
+        <v>1228</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1478</v>
+        <v>1546</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1249</v>
+        <v>1233</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1252</v>
+        <v>1267</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>196</v>
+        <v>141</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1218</v>
+        <v>1295</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1556</v>
+        <v>1477</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1225</v>
+        <v>1248</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1276</v>
+        <v>1251</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>219</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1520</v>
+        <v>1216</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1254</v>
+        <v>1556</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1302</v>
+        <v>1225</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1199</v>
+        <v>1274</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>277</v>
+        <v>107</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>98</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1481</v>
+        <v>1518</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1289</v>
+        <v>1254</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1271</v>
+        <v>1301</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1228</v>
+        <v>1198</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>325</v>
+        <v>277</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1212</v>
+        <v>1479</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1557</v>
+        <v>1289</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1207</v>
+        <v>1271</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1289</v>
+        <v>1226</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>961</v>
+        <v>1211</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1808</v>
+        <v>1556</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1132</v>
+        <v>1206</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1364</v>
+        <v>1288</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>689</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1552</v>
+        <v>960</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1216</v>
+        <v>1807</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1278</v>
+        <v>1131</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1218</v>
+        <v>1363</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>229</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1707</v>
+        <v>1550</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1061</v>
+        <v>1216</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1310</v>
+        <v>1277</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1184</v>
+        <v>1217</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>173</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1757</v>
+        <v>1705</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1011</v>
+        <v>1061</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>126</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1779</v>
+        <v>1755</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>989</v>
+        <v>1011</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>325</v>
+        <v>218</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>89</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1626</v>
+        <v>1777</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1142</v>
+        <v>989</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1226</v>
+        <v>1301</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1265</v>
+        <v>1190</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>123</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1178</v>
+        <v>1099</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1602</v>
+        <v>1686</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1239</v>
+        <v>1216</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1283</v>
+        <v>1310</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>272</v>
+        <v>111</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>105</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>962</v>
+        <v>1176</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1817</v>
+        <v>1605</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1178</v>
+        <v>1239</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1342</v>
+        <v>1284</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>127</v>
+        <v>272</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>270</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1138</v>
+        <v>960</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1638</v>
+        <v>1820</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1228</v>
+        <v>1178</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1290</v>
+        <v>1343</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>341</v>
+        <v>127</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>106</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>867</v>
+        <v>1137</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1909</v>
+        <v>1640</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1164</v>
+        <v>1228</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1352</v>
+        <v>1291</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>183</v>
+        <v>340</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1176</v>
+        <v>1164</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1336</v>
+        <v>1353</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>201</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1080</v>
+        <v>867</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1695</v>
+        <v>1909</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1209</v>
+        <v>1176</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1299</v>
+        <v>1337</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1379</v>
+        <v>1080</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1395</v>
+        <v>1696</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1288</v>
+        <v>1209</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1218</v>
+        <v>1300</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>204</v>
+        <v>127</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>92</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1278</v>
+        <v>1380</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1496</v>
+        <v>1395</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1259</v>
+        <v>1288</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1244</v>
+        <v>1219</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>119</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1179</v>
+        <v>1279</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1595</v>
+        <v>1496</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1231</v>
+        <v>1259</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1271</v>
+        <v>1245</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>99</v>
+        <v>209</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>212</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1228</v>
+        <v>1181</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1546</v>
+        <v>1594</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>121</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1295</v>
+        <v>1229</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1477</v>
+        <v>1546</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1248</v>
+        <v>1233</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1251</v>
+        <v>1268</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1216</v>
+        <v>1296</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1556</v>
+        <v>1477</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1225</v>
+        <v>1248</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1274</v>
+        <v>1252</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>219</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1518</v>
+        <v>1217</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1254</v>
+        <v>1556</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1301</v>
+        <v>1225</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1198</v>
+        <v>1275</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>277</v>
+        <v>106</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>99</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1479</v>
+        <v>1519</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1289</v>
+        <v>1254</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1271</v>
+        <v>1301</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1226</v>
+        <v>1199</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1211</v>
+        <v>1479</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1556</v>
+        <v>1290</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1206</v>
+        <v>1271</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1288</v>
+        <v>1227</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>421</v>
+        <v>325</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>960</v>
+        <v>1211</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1807</v>
+        <v>1557</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1131</v>
+        <v>1206</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1363</v>
+        <v>1289</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>689</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1550</v>
+        <v>960</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1216</v>
+        <v>1808</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1277</v>
+        <v>1131</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1217</v>
+        <v>1364</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>229</v>
+        <v>689</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1705</v>
+        <v>1551</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1061</v>
+        <v>1216</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1309</v>
+        <v>1278</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1183</v>
+        <v>1217</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1755</v>
+        <v>1706</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1011</v>
+        <v>1061</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>125</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1777</v>
+        <v>1756</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>989</v>
+        <v>1011</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>325</v>
+        <v>217</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>89</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1099</v>
+        <v>1258</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1686</v>
+        <v>1529</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1216</v>
+        <v>1254</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1310</v>
+        <v>1272</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>197</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1176</v>
+        <v>1099</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1605</v>
+        <v>1686</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1239</v>
+        <v>1215</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1284</v>
+        <v>1310</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>272</v>
+        <v>112</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>105</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>960</v>
+        <v>1177</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1820</v>
+        <v>1604</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1178</v>
+        <v>1238</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1343</v>
+        <v>1284</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>127</v>
+        <v>271</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>269</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1137</v>
+        <v>960</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1640</v>
+        <v>1820</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1228</v>
+        <v>1177</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1291</v>
+        <v>1343</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>340</v>
+        <v>128</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>106</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>867</v>
+        <v>1137</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1910</v>
+        <v>1640</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1164</v>
+        <v>1227</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1353</v>
+        <v>1291</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>182</v>
+        <v>341</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>1909</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1337</v>
+        <v>1353</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>200</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1080</v>
+        <v>868</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1696</v>
+        <v>1908</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1209</v>
+        <v>1175</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1300</v>
+        <v>1337</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>270</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1380</v>
+        <v>1079</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1395</v>
+        <v>1697</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1288</v>
+        <v>1207</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1219</v>
+        <v>1301</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>204</v>
+        <v>127</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>93</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1279</v>
+        <v>1379</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1496</v>
+        <v>1396</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1259</v>
+        <v>1286</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1245</v>
+        <v>1220</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>119</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1181</v>
+        <v>1279</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1594</v>
+        <v>1496</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1231</v>
+        <v>1257</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1272</v>
+        <v>1246</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>212</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>1181</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1594</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>1229</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>1546</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>1233</v>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>121</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1296</v>
+        <v>1230</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1477</v>
+        <v>1545</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1248</v>
+        <v>1231</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1252</v>
+        <v>1269</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>196</v>
+        <v>142</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1217</v>
+        <v>1296</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1556</v>
+        <v>1477</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1225</v>
+        <v>1246</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1275</v>
+        <v>1253</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>218</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1519</v>
+        <v>1219</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1254</v>
+        <v>1554</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1301</v>
+        <v>1222</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1199</v>
+        <v>1277</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>276</v>
+        <v>106</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>99</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1479</v>
+        <v>1518</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1290</v>
+        <v>1255</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1271</v>
+        <v>1300</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1227</v>
+        <v>1199</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1211</v>
+        <v>1478</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1557</v>
+        <v>1291</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1206</v>
+        <v>1269</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1289</v>
+        <v>1228</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>420</v>
+        <v>326</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>960</v>
+        <v>1212</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1808</v>
+        <v>1556</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1131</v>
+        <v>1204</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1364</v>
+        <v>1290</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>689</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1551</v>
+        <v>960</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1216</v>
+        <v>1808</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1278</v>
+        <v>1129</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1217</v>
+        <v>1365</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>229</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1706</v>
+        <v>1550</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1061</v>
+        <v>1217</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1309</v>
+        <v>1276</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1184</v>
+        <v>1218</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>211</v>
+        <v>115</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1756</v>
+        <v>1707</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1011</v>
+        <v>1060</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1258</v>
+        <v>1603</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1529</v>
+        <v>1205</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1254</v>
+        <v>1355</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1272</v>
+        <v>1194</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>292</v>
+        <v>486</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1099</v>
+        <v>1268</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1686</v>
+        <v>1540</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1215</v>
+        <v>1261</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1310</v>
+        <v>1287</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>112</v>
+        <v>297</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1177</v>
+        <v>1107</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1604</v>
+        <v>1699</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1238</v>
+        <v>1223</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1284</v>
+        <v>1324</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>271</v>
+        <v>120</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>106</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>960</v>
+        <v>1183</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1820</v>
+        <v>1619</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1177</v>
+        <v>1245</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1343</v>
+        <v>1299</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>128</v>
+        <v>275</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>270</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1137</v>
+        <v>966</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1640</v>
+        <v>1835</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1227</v>
+        <v>1184</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1291</v>
+        <v>1358</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>341</v>
+        <v>132</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>106</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>868</v>
+        <v>1145</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1909</v>
+        <v>1653</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1163</v>
+        <v>1235</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1353</v>
+        <v>1305</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>181</v>
+        <v>347</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1908</v>
+        <v>1921</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1337</v>
+        <v>1367</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>199</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1079</v>
+        <v>879</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1697</v>
+        <v>1918</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1301</v>
+        <v>1351</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>270</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1379</v>
+        <v>1090</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1396</v>
+        <v>1707</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1286</v>
+        <v>1216</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1220</v>
+        <v>1314</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>94</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1279</v>
+        <v>1389</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1496</v>
+        <v>1407</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1257</v>
+        <v>1295</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1246</v>
+        <v>1233</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1181</v>
+        <v>1290</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1594</v>
+        <v>1506</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1229</v>
+        <v>1264</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>212</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1230</v>
+        <v>1187</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1545</v>
+        <v>1609</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1231</v>
+        <v>1236</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1269</v>
+        <v>1288</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1296</v>
+        <v>1237</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1477</v>
+        <v>1559</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1253</v>
+        <v>1283</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1219</v>
+        <v>1302</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1554</v>
+        <v>1492</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1222</v>
+        <v>1256</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>106</v>
+        <v>206</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>218</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1518</v>
+        <v>1227</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1255</v>
+        <v>1567</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1199</v>
+        <v>1291</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>276</v>
+        <v>111</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>99</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1478</v>
+        <v>1525</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1291</v>
+        <v>1269</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1269</v>
+        <v>1309</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1228</v>
+        <v>1212</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1212</v>
+        <v>1483</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1556</v>
+        <v>1307</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1204</v>
+        <v>1278</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1290</v>
+        <v>1241</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>421</v>
+        <v>333</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>960</v>
+        <v>1217</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1808</v>
+        <v>1572</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1129</v>
+        <v>1212</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1365</v>
+        <v>1304</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>689</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1550</v>
+        <v>968</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1217</v>
+        <v>1821</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1276</v>
+        <v>1138</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1218</v>
+        <v>1378</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>231</v>
+        <v>701</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1707</v>
+        <v>1558</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1060</v>
+        <v>1230</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1307</v>
+        <v>1285</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1185</v>
+        <v>1231</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1205</v>
+        <v>1191</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1194</v>
+        <v>1179</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>486</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>99</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1268</v>
+        <v>1597</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1540</v>
+        <v>1195</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1261</v>
+        <v>1349</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1287</v>
+        <v>1185</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>297</v>
+        <v>485</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1107</v>
+        <v>1258</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1699</v>
+        <v>1534</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1223</v>
+        <v>1256</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1324</v>
+        <v>1277</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>120</v>
+        <v>294</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>202</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1183</v>
+        <v>1101</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1245</v>
+        <v>1217</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1299</v>
+        <v>1315</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>115</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>966</v>
+        <v>1176</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1835</v>
+        <v>1610</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1184</v>
+        <v>1240</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1358</v>
+        <v>1289</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>279</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1145</v>
+        <v>961</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1653</v>
+        <v>1824</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1235</v>
+        <v>1179</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1305</v>
+        <v>1348</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>347</v>
+        <v>128</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>114</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>877</v>
+        <v>1139</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1921</v>
+        <v>1643</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1171</v>
+        <v>1229</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1367</v>
+        <v>1296</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>185</v>
+        <v>343</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1918</v>
+        <v>1912</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1183</v>
+        <v>1165</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>206</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1090</v>
+        <v>873</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1707</v>
+        <v>1908</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1216</v>
+        <v>1178</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1314</v>
+        <v>1341</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1389</v>
+        <v>1085</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1407</v>
+        <v>1696</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1295</v>
+        <v>1210</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1233</v>
+        <v>1305</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>96</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1290</v>
+        <v>1383</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1506</v>
+        <v>1397</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1264</v>
+        <v>1289</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1261</v>
+        <v>1224</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1187</v>
+        <v>1283</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1609</v>
+        <v>1497</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1236</v>
+        <v>1260</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1288</v>
+        <v>1250</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>108</v>
+        <v>213</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1237</v>
+        <v>1183</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1559</v>
+        <v>1597</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>125</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1302</v>
+        <v>1233</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1492</v>
+        <v>1547</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1256</v>
+        <v>1234</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>206</v>
+        <v>147</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1227</v>
+        <v>1296</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1567</v>
+        <v>1482</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1230</v>
+        <v>1250</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1291</v>
+        <v>1256</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>226</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1525</v>
+        <v>1221</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1269</v>
+        <v>1557</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1309</v>
+        <v>1225</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1212</v>
+        <v>1281</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>282</v>
+        <v>107</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>107</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1483</v>
+        <v>1520</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1307</v>
+        <v>1258</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1278</v>
+        <v>1304</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1241</v>
+        <v>1202</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1217</v>
+        <v>1480</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1572</v>
+        <v>1294</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1212</v>
+        <v>1273</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1304</v>
+        <v>1231</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>426</v>
+        <v>326</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>968</v>
+        <v>1214</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1821</v>
+        <v>1559</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1138</v>
+        <v>1207</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1378</v>
+        <v>1294</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>86</v>
+        <v>423</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>701</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1558</v>
+        <v>966</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1230</v>
+        <v>1807</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1285</v>
+        <v>1133</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1231</v>
+        <v>1368</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>241</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1602</v>
+        <v>1726</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1191</v>
+        <v>1067</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1356</v>
+        <v>1401</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1179</v>
+        <v>1134</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>485</v>
+        <v>223</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>92</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1258</v>
+        <v>1599</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1534</v>
+        <v>1193</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1256</v>
+        <v>1348</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1277</v>
+        <v>1184</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>294</v>
+        <v>484</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1101</v>
+        <v>1259</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1689</v>
+        <v>1533</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1217</v>
+        <v>1255</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1315</v>
+        <v>1276</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>198</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1176</v>
+        <v>1103</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1610</v>
+        <v>1687</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1240</v>
+        <v>1216</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1289</v>
+        <v>1314</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>271</v>
+        <v>117</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>108</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>961</v>
+        <v>1176</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1824</v>
+        <v>1610</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1179</v>
+        <v>1239</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1348</v>
+        <v>1288</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>128</v>
+        <v>272</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>275</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1139</v>
+        <v>961</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1643</v>
+        <v>1824</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1229</v>
+        <v>1178</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1296</v>
+        <v>1347</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>108</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>870</v>
+        <v>1140</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1912</v>
+        <v>1642</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1165</v>
+        <v>1228</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1358</v>
+        <v>1295</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1908</v>
+        <v>1912</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1178</v>
+        <v>1164</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1341</v>
+        <v>1357</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>204</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1085</v>
+        <v>874</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1696</v>
+        <v>1907</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1210</v>
+        <v>1177</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1305</v>
+        <v>1340</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>269</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1383</v>
+        <v>1085</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1397</v>
+        <v>1696</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1289</v>
+        <v>1209</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1224</v>
+        <v>1304</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>93</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1283</v>
+        <v>1384</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1497</v>
+        <v>1396</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1260</v>
+        <v>1288</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1250</v>
+        <v>1223</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>120</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1183</v>
+        <v>1284</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1597</v>
+        <v>1496</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1232</v>
+        <v>1259</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1277</v>
+        <v>1249</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>105</v>
+        <v>213</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1233</v>
+        <v>1184</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1547</v>
+        <v>1596</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>120</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1296</v>
+        <v>1234</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1482</v>
+        <v>1546</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1250</v>
+        <v>1233</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1256</v>
+        <v>1272</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1221</v>
+        <v>1298</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1557</v>
+        <v>1480</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1225</v>
+        <v>1249</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1281</v>
+        <v>1255</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>222</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1520</v>
+        <v>1221</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1258</v>
+        <v>1557</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1304</v>
+        <v>1224</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1202</v>
+        <v>1280</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>278</v>
+        <v>107</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>102</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1480</v>
+        <v>1519</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1294</v>
+        <v>1259</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1273</v>
+        <v>1303</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1231</v>
+        <v>1201</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>326</v>
+        <v>279</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1214</v>
+        <v>1479</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1559</v>
+        <v>1295</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1207</v>
+        <v>1271</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1294</v>
+        <v>1231</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>423</v>
+        <v>325</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>966</v>
+        <v>1212</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1807</v>
+        <v>1561</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1133</v>
+        <v>1206</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1368</v>
+        <v>1293</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>84</v>
+        <v>424</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>692</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1726</v>
+        <v>1720</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1401</v>
+        <v>1422</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1134</v>
+        <v>1114</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>275</v>
+        <v>221</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1603</v>
+        <v>1725</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1190</v>
+        <v>1066</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1355</v>
+        <v>1403</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1178</v>
+        <v>1132</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1348</v>
+        <v>1357</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>484</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>92</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1259</v>
+        <v>1599</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1533</v>
+        <v>1191</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1255</v>
+        <v>1350</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1276</v>
+        <v>1182</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>294</v>
+        <v>482</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1103</v>
+        <v>1259</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1687</v>
+        <v>1531</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1216</v>
+        <v>1257</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1314</v>
+        <v>1274</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>117</v>
+        <v>293</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>198</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1176</v>
+        <v>1104</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1610</v>
+        <v>1684</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1239</v>
+        <v>1218</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1288</v>
+        <v>1312</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>272</v>
+        <v>117</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>107</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1824</v>
+        <v>1607</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1178</v>
+        <v>1241</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1347</v>
+        <v>1286</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>275</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1140</v>
+        <v>961</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1642</v>
+        <v>1822</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1228</v>
+        <v>1180</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1295</v>
+        <v>1345</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>108</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>870</v>
+        <v>1141</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1912</v>
+        <v>1639</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1164</v>
+        <v>1230</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1357</v>
+        <v>1293</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>182</v>
+        <v>342</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1340</v>
+        <v>1355</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>204</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1085</v>
+        <v>875</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1696</v>
+        <v>1904</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1209</v>
+        <v>1179</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1304</v>
+        <v>1338</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>270</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1384</v>
+        <v>1086</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1396</v>
+        <v>1693</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1288</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1223</v>
+        <v>1302</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>93</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1284</v>
+        <v>1384</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1496</v>
+        <v>1394</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1259</v>
+        <v>1290</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1249</v>
+        <v>1221</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>120</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1184</v>
+        <v>1284</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1596</v>
+        <v>1494</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1231</v>
+        <v>1261</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1276</v>
+        <v>1247</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>105</v>
+        <v>213</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1234</v>
+        <v>1185</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1546</v>
+        <v>1593</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>1233</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>119</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1298</v>
+        <v>1234</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1480</v>
+        <v>1544</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1249</v>
+        <v>1235</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1255</v>
+        <v>1270</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1221</v>
+        <v>1299</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1557</v>
+        <v>1477</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1224</v>
+        <v>1251</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1280</v>
+        <v>1253</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>222</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1519</v>
+        <v>1222</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1259</v>
+        <v>1554</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1303</v>
+        <v>1226</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1201</v>
+        <v>1278</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>279</v>
+        <v>107</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>101</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1479</v>
+        <v>1520</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1295</v>
+        <v>1256</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1271</v>
+        <v>1305</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1231</v>
+        <v>1199</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1212</v>
+        <v>1480</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1561</v>
+        <v>1292</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1206</v>
+        <v>1273</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1293</v>
+        <v>1229</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>424</v>
+        <v>323</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1720</v>
+        <v>1695</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1072</v>
+        <v>1097</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1422</v>
+        <v>1431</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1725</v>
+        <v>1719</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1403</v>
+        <v>1421</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1132</v>
+        <v>1115</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>273</v>
+        <v>222</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1603</v>
+        <v>1725</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1188</v>
+        <v>1066</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1357</v>
+        <v>1402</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1176</v>
+        <v>1133</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>482</v>
+        <v>223</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>92</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1259</v>
+        <v>1600</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1531</v>
+        <v>1190</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1257</v>
+        <v>1349</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1274</v>
+        <v>1183</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>293</v>
+        <v>482</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1104</v>
+        <v>1259</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1684</v>
+        <v>1531</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1218</v>
+        <v>1256</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1312</v>
+        <v>1275</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>117</v>
+        <v>293</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>198</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1177</v>
+        <v>1104</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1607</v>
+        <v>1684</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1241</v>
+        <v>1217</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1286</v>
+        <v>1313</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>271</v>
+        <v>117</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>107</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1822</v>
+        <v>1607</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1180</v>
+        <v>1240</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1345</v>
+        <v>1287</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>275</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1141</v>
+        <v>960</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1639</v>
+        <v>1823</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1230</v>
+        <v>1179</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1293</v>
+        <v>1346</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>342</v>
+        <v>130</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>108</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>870</v>
+        <v>1140</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1910</v>
+        <v>1640</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1166</v>
+        <v>1229</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1355</v>
+        <v>1294</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>182</v>
+        <v>342</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1904</v>
+        <v>1911</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1179</v>
+        <v>1165</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1338</v>
+        <v>1356</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>203</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1086</v>
+        <v>873</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1693</v>
+        <v>1906</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1211</v>
+        <v>1177</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1302</v>
+        <v>1340</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>270</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1384</v>
+        <v>1084</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1394</v>
+        <v>1695</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1290</v>
+        <v>1210</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1221</v>
+        <v>1303</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>92</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1284</v>
+        <v>1383</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1494</v>
+        <v>1395</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1261</v>
+        <v>1289</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1247</v>
+        <v>1222</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>120</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1185</v>
+        <v>1283</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1593</v>
+        <v>1495</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1233</v>
+        <v>1260</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1274</v>
+        <v>1248</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>105</v>
+        <v>213</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1234</v>
+        <v>1184</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1544</v>
+        <v>1594</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>119</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1299</v>
+        <v>1232</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1477</v>
+        <v>1546</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1251</v>
+        <v>1234</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1253</v>
+        <v>1271</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1222</v>
+        <v>1297</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1554</v>
+        <v>1479</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1226</v>
+        <v>1249</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1278</v>
+        <v>1255</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>107</v>
+        <v>199</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>221</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1520</v>
+        <v>1220</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1256</v>
+        <v>1556</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1305</v>
+        <v>1225</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1199</v>
+        <v>1279</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>279</v>
+        <v>106</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>100</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1480</v>
+        <v>1519</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1292</v>
+        <v>1257</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1273</v>
+        <v>1303</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1229</v>
+        <v>1201</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1695</v>
+        <v>1666</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1097</v>
+        <v>1167</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1431</v>
+        <v>1448</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1110</v>
+        <v>1129</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>179</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1073</v>
+        <v>1117</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1421</v>
+        <v>1448</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>156</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1725</v>
+        <v>1739</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1066</v>
+        <v>1093</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1402</v>
+        <v>1437</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>1133</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1603</v>
+        <v>1743</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1188</v>
+        <v>1088</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1356</v>
+        <v>1419</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1177</v>
+        <v>1150</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>223</v>
+        <v>282</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1600</v>
+        <v>1619</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1190</v>
+        <v>1212</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1183</v>
+        <v>1195</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>482</v>
+        <v>231</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1259</v>
+        <v>1619</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1531</v>
+        <v>1211</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1256</v>
+        <v>1365</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1275</v>
+        <v>1201</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>293</v>
+        <v>487</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1104</v>
+        <v>1281</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1684</v>
+        <v>1549</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1217</v>
+        <v>1273</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1313</v>
+        <v>1292</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>117</v>
+        <v>306</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>198</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1177</v>
+        <v>1125</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1607</v>
+        <v>1703</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1287</v>
+        <v>1330</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>106</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>960</v>
+        <v>1197</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1823</v>
+        <v>1627</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1179</v>
+        <v>1256</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1346</v>
+        <v>1305</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>130</v>
+        <v>275</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>274</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1140</v>
+        <v>980</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1640</v>
+        <v>1843</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1229</v>
+        <v>1196</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1294</v>
+        <v>1363</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>110</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>869</v>
+        <v>1159</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1911</v>
+        <v>1661</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1165</v>
+        <v>1246</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1356</v>
+        <v>1311</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>183</v>
+        <v>350</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1906</v>
+        <v>1931</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1340</v>
+        <v>1374</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>202</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1084</v>
+        <v>890</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1695</v>
+        <v>1928</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1210</v>
+        <v>1191</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1303</v>
+        <v>1360</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>270</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1383</v>
+        <v>1101</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1395</v>
+        <v>1717</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1289</v>
+        <v>1226</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1222</v>
+        <v>1321</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>92</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1283</v>
+        <v>1402</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1495</v>
+        <v>1415</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1260</v>
+        <v>1305</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1184</v>
+        <v>1303</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1594</v>
+        <v>1513</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1232</v>
+        <v>1276</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1275</v>
+        <v>1266</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>213</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1232</v>
+        <v>1204</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1546</v>
+        <v>1612</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1234</v>
+        <v>1248</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1271</v>
+        <v>1293</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>119</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1297</v>
+        <v>1250</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1479</v>
+        <v>1566</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1255</v>
+        <v>1287</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1220</v>
+        <v>1314</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1556</v>
+        <v>1500</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1225</v>
+        <v>1265</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>106</v>
+        <v>204</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>221</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1519</v>
+        <v>1237</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1257</v>
+        <v>1577</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1303</v>
+        <v>1243</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1201</v>
+        <v>1295</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>99</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1666</v>
+        <v>1608</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1167</v>
+        <v>1226</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1448</v>
+        <v>1432</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1129</v>
+        <v>1146</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>240</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1715</v>
+        <v>1666</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1117</v>
+        <v>1167</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>1448</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>192</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1739</v>
+        <v>1716</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1093</v>
+        <v>1116</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1437</v>
+        <v>1447</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>170</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1743</v>
+        <v>1737</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1419</v>
+        <v>1438</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1150</v>
+        <v>1132</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>126</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1619</v>
+        <v>1741</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1212</v>
+        <v>1090</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1372</v>
+        <v>1418</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1195</v>
+        <v>1151</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>487</v>
+        <v>230</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>103</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1281</v>
+        <v>1622</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1549</v>
+        <v>1208</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1273</v>
+        <v>1366</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1292</v>
+        <v>1200</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>306</v>
+        <v>489</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1125</v>
+        <v>1280</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1703</v>
+        <v>1550</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1234</v>
+        <v>1273</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1330</v>
+        <v>1292</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>123</v>
+        <v>304</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>209</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1197</v>
+        <v>1122</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1627</v>
+        <v>1706</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1256</v>
+        <v>1233</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1305</v>
+        <v>1331</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>113</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>980</v>
+        <v>1197</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1843</v>
+        <v>1627</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1196</v>
+        <v>1257</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1363</v>
+        <v>1304</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>134</v>
+        <v>276</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>284</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1159</v>
+        <v>979</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1661</v>
+        <v>1844</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1246</v>
+        <v>1196</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1311</v>
+        <v>1363</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>350</v>
+        <v>138</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>115</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>888</v>
+        <v>1159</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1931</v>
+        <v>1660</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1181</v>
+        <v>1244</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1374</v>
+        <v>1313</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1928</v>
+        <v>1933</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1191</v>
+        <v>1180</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1360</v>
+        <v>1375</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>213</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1101</v>
+        <v>892</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1717</v>
+        <v>1926</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1226</v>
+        <v>1193</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1321</v>
+        <v>1358</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>280</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1402</v>
+        <v>1103</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1415</v>
+        <v>1715</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1305</v>
+        <v>1226</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1240</v>
+        <v>1321</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>102</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1303</v>
+        <v>1402</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1513</v>
+        <v>1414</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1276</v>
+        <v>1305</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1266</v>
+        <v>1240</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1204</v>
+        <v>1302</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1612</v>
+        <v>1514</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1248</v>
+        <v>1276</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1293</v>
+        <v>1266</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>221</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1250</v>
+        <v>1201</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1566</v>
+        <v>1615</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>124</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1314</v>
+        <v>1251</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1500</v>
+        <v>1565</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1265</v>
+        <v>1251</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1273</v>
+        <v>1288</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1237</v>
+        <v>1314</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1577</v>
+        <v>1500</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1243</v>
+        <v>1266</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1295</v>
+        <v>1272</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>233</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1608</v>
+        <v>1542</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1226</v>
+        <v>1294</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1432</v>
+        <v>1401</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1146</v>
+        <v>1177</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>206</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1666</v>
+        <v>1605</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1167</v>
+        <v>1229</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1448</v>
+        <v>1433</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1129</v>
+        <v>1145</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>234</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1716</v>
+        <v>1668</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1116</v>
+        <v>1165</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>1447</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>215</v>
+        <v>272</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>195</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1737</v>
+        <v>1714</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1095</v>
+        <v>1118</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1438</v>
+        <v>1447</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>167</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1741</v>
+        <v>1735</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1418</v>
+        <v>1437</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1151</v>
+        <v>1133</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>127</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1622</v>
+        <v>1744</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1209</v>
+        <v>1087</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1372</v>
+        <v>1418</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1195</v>
+        <v>1151</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>489</v>
+        <v>233</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1280</v>
+        <v>1621</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1550</v>
+        <v>1209</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1273</v>
+        <v>1366</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1292</v>
+        <v>1200</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>304</v>
+        <v>486</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1122</v>
+        <v>1277</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1706</v>
+        <v>1553</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1233</v>
+        <v>1272</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1331</v>
+        <v>1293</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>208</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1197</v>
+        <v>1123</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1627</v>
+        <v>1705</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1257</v>
+        <v>1235</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1304</v>
+        <v>1329</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>276</v>
+        <v>123</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>114</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>979</v>
+        <v>1195</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1844</v>
+        <v>1629</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1196</v>
+        <v>1256</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1363</v>
+        <v>1305</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>138</v>
+        <v>281</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>279</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1159</v>
+        <v>978</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1660</v>
+        <v>1844</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1244</v>
+        <v>1194</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1313</v>
+        <v>1365</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>347</v>
+        <v>133</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>118</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>886</v>
+        <v>1157</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1933</v>
+        <v>1662</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1180</v>
+        <v>1243</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1375</v>
+        <v>1314</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>192</v>
+        <v>351</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1926</v>
+        <v>1932</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1358</v>
+        <v>1373</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>211</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1103</v>
+        <v>894</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1715</v>
+        <v>1924</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1226</v>
+        <v>1193</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1321</v>
+        <v>1358</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>281</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1402</v>
+        <v>1105</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1414</v>
+        <v>1712</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1305</v>
+        <v>1226</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1240</v>
+        <v>1321</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>212</v>
+        <v>139</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>100</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1302</v>
+        <v>1400</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1514</v>
+        <v>1416</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1276</v>
+        <v>1305</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1266</v>
+        <v>1240</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>127</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1201</v>
+        <v>1300</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1615</v>
+        <v>1516</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1249</v>
+        <v>1278</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1292</v>
+        <v>1264</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>115</v>
+        <v>224</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>221</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1251</v>
+        <v>1201</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1565</v>
+        <v>1615</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>126</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1314</v>
+        <v>1252</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1500</v>
+        <v>1564</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1266</v>
+        <v>1253</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1272</v>
+        <v>1286</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Screener Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screener Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1542</v>
+        <v>1553</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1294</v>
+        <v>1283</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1401</v>
+        <v>1415</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>204</v>
+        <v>273</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>257</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1605</v>
+        <v>1541</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1229</v>
+        <v>1295</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1433</v>
+        <v>1401</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1145</v>
+        <v>1177</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>200</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1668</v>
+        <v>1606</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1165</v>
+        <v>1228</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1447</v>
+        <v>1432</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1130</v>
+        <v>1146</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>236</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1714</v>
+        <v>1665</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1118</v>
+        <v>1168</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>193</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1735</v>
+        <v>1713</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1097</v>
+        <v>1119</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1437</v>
+        <v>1446</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1744</v>
+        <v>1738</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1418</v>
+        <v>1437</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1151</v>
+        <v>1133</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>279</v>
+        <v>229</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>124</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1626</v>
+        <v>1747</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1205</v>
+        <v>1084</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1373</v>
+        <v>1419</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>486</v>
+        <v>231</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>102</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1277</v>
+        <v>1618</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1553</v>
+        <v>1212</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1272</v>
+        <v>1365</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1293</v>
+        <v>1201</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>303</v>
+        <v>484</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1123</v>
+        <v>1279</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1705</v>
+        <v>1551</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1235</v>
+        <v>1273</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1329</v>
+        <v>1292</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>123</v>
+        <v>305</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>207</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1195</v>
+        <v>1121</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1629</v>
+        <v>1707</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1256</v>
+        <v>1235</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1305</v>
+        <v>1329</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>281</v>
+        <v>127</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>109</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>978</v>
+        <v>1194</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1844</v>
+        <v>1629</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1194</v>
+        <v>1254</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1365</v>
+        <v>1307</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>133</v>
+        <v>277</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>283</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1157</v>
+        <v>977</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1662</v>
+        <v>1845</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1243</v>
+        <v>1193</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1314</v>
+        <v>1366</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>351</v>
+        <v>137</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>122</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>887</v>
+        <v>1157</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1932</v>
+        <v>1662</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1182</v>
+        <v>1245</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1373</v>
+        <v>1312</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>190</v>
+        <v>348</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1924</v>
+        <v>1930</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1358</v>
+        <v>1373</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>213</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1105</v>
+        <v>897</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1712</v>
+        <v>1920</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1226</v>
+        <v>1193</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1321</v>
+        <v>1358</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>278</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1400</v>
+        <v>1102</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1416</v>
+        <v>1715</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1305</v>
+        <v>1226</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1240</v>
+        <v>1321</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>99</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1300</v>
+        <v>1397</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1516</v>
+        <v>1419</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1278</v>
+        <v>1306</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1264</v>
+        <v>1239</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1201</v>
+        <v>1301</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1615</v>
+        <v>1515</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1247</v>
+        <v>1277</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1294</v>
+        <v>1265</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>225</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1252</v>
+        <v>1202</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1564</v>
+        <v>1614</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1286</v>
+        <v>1293</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>128</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1553</v>
+        <v>1475</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1283</v>
+        <v>1362</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1415</v>
+        <v>1396</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1163</v>
+        <v>1183</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>273</v>
+        <v>212</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>200</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1541</v>
+        <v>1552</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1295</v>
+        <v>1284</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1401</v>
+        <v>1415</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>251</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1606</v>
+        <v>1543</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1228</v>
+        <v>1293</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1432</v>
+        <v>1400</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1146</v>
+        <v>1178</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>203</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1665</v>
+        <v>1605</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1168</v>
+        <v>1229</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1448</v>
+        <v>1433</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1129</v>
+        <v>1145</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>233</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1713</v>
+        <v>1664</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1119</v>
+        <v>1169</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>194</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1738</v>
+        <v>1716</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1094</v>
+        <v>1116</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1437</v>
+        <v>1446</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1747</v>
+        <v>1740</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1419</v>
+        <v>1438</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1150</v>
+        <v>1132</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>281</v>
+        <v>231</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1625</v>
+        <v>1747</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1206</v>
+        <v>1084</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1373</v>
+        <v>1419</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>484</v>
+        <v>228</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1279</v>
+        <v>1619</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1551</v>
+        <v>1211</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1273</v>
+        <v>1366</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1292</v>
+        <v>1200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>305</v>
+        <v>485</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1121</v>
+        <v>1277</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1707</v>
+        <v>1553</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1235</v>
+        <v>1273</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1329</v>
+        <v>1292</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>127</v>
+        <v>309</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>202</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1194</v>
+        <v>1120</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1629</v>
+        <v>1707</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1254</v>
+        <v>1233</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1307</v>
+        <v>1331</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>277</v>
+        <v>124</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>113</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>977</v>
+        <v>1191</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1845</v>
+        <v>1632</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1193</v>
+        <v>1253</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1366</v>
+        <v>1308</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>286</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1157</v>
+        <v>979</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1662</v>
+        <v>1843</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1245</v>
+        <v>1195</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1312</v>
+        <v>1364</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>348</v>
+        <v>135</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>121</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>889</v>
+        <v>1159</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1930</v>
+        <v>1660</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1182</v>
+        <v>1245</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1373</v>
+        <v>1312</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>190</v>
+        <v>350</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1920</v>
+        <v>1927</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1358</v>
+        <v>1373</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>210</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1102</v>
+        <v>895</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1715</v>
+        <v>1922</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1226</v>
+        <v>1193</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1321</v>
+        <v>1358</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>276</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1397</v>
+        <v>1099</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1419</v>
+        <v>1718</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1306</v>
+        <v>1227</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1239</v>
+        <v>1320</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>99</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1301</v>
+        <v>1397</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1515</v>
+        <v>1419</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1277</v>
+        <v>1305</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1265</v>
+        <v>1240</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>129</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1202</v>
+        <v>1301</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1614</v>
+        <v>1515</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1248</v>
+        <v>1278</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1293</v>
+        <v>1264</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>228</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1475</v>
+        <v>1425</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1362</v>
+        <v>1415</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1552</v>
+        <v>1474</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1284</v>
+        <v>1363</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1415</v>
+        <v>1394</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1163</v>
+        <v>1183</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>194</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1178</v>
+        <v>1159</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>256</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1605</v>
+        <v>1544</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1229</v>
+        <v>1292</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1433</v>
+        <v>1401</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1145</v>
+        <v>1173</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>199</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1664</v>
+        <v>1604</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1169</v>
+        <v>1230</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1447</v>
+        <v>1431</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>234</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1716</v>
+        <v>1662</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1116</v>
+        <v>1165</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>1446</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>192</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1740</v>
+        <v>1716</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1092</v>
+        <v>1116</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>167</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1747</v>
+        <v>1739</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1419</v>
+        <v>1435</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1150</v>
+        <v>1132</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>280</v>
+        <v>231</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>121</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1621</v>
+        <v>1746</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1210</v>
+        <v>1082</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1372</v>
+        <v>1416</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1195</v>
+        <v>1147</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>485</v>
+        <v>231</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1277</v>
+        <v>1617</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1553</v>
+        <v>1209</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1273</v>
+        <v>1366</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1292</v>
+        <v>1197</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>309</v>
+        <v>484</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1120</v>
+        <v>1277</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1707</v>
+        <v>1552</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1233</v>
+        <v>1274</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1331</v>
+        <v>1291</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>124</v>
+        <v>307</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>205</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1191</v>
+        <v>1115</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1632</v>
+        <v>1708</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1253</v>
+        <v>1231</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1308</v>
+        <v>1330</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>279</v>
+        <v>127</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>118</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>979</v>
+        <v>1186</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1843</v>
+        <v>1632</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1195</v>
+        <v>1251</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1364</v>
+        <v>1304</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>285</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1159</v>
+        <v>980</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1660</v>
+        <v>1842</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1245</v>
+        <v>1194</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1312</v>
+        <v>1365</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>350</v>
+        <v>134</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>122</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>891</v>
+        <v>1155</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1927</v>
+        <v>1656</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1182</v>
+        <v>1243</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1373</v>
+        <v>1311</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>190</v>
+        <v>349</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1922</v>
+        <v>1928</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1358</v>
+        <v>1373</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>207</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1099</v>
+        <v>893</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1718</v>
+        <v>1924</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1227</v>
+        <v>1191</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1320</v>
+        <v>1357</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>276</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1397</v>
+        <v>1094</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1419</v>
+        <v>1717</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1305</v>
+        <v>1226</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1240</v>
+        <v>1321</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>101</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1301</v>
+        <v>1398</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1515</v>
+        <v>1417</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1278</v>
+        <v>1307</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1264</v>
+        <v>1235</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,309 +523,309 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1425</v>
+        <v>1338</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1415</v>
+        <v>1495</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1398</v>
+        <v>1379</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1179</v>
+        <v>1198</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>232</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1474</v>
+        <v>1420</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1363</v>
+        <v>1411</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1546</v>
+        <v>1473</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1281</v>
+        <v>1360</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1413</v>
+        <v>1396</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1159</v>
+        <v>1179</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>266</v>
+        <v>209</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1544</v>
+        <v>1553</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1292</v>
+        <v>1279</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1401</v>
+        <v>1414</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1173</v>
+        <v>1164</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>198</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1604</v>
+        <v>1541</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1230</v>
+        <v>1295</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1431</v>
+        <v>1402</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1141</v>
+        <v>1176</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>197</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1662</v>
+        <v>1608</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1165</v>
+        <v>1223</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1446</v>
+        <v>1430</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1131</v>
+        <v>1142</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>233</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1716</v>
+        <v>1662</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1116</v>
+        <v>1162</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1446</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>190</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1739</v>
+        <v>1717</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1093</v>
+        <v>1112</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1435</v>
+        <v>1447</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>166</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1746</v>
+        <v>1738</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1416</v>
+        <v>1435</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1147</v>
+        <v>1129</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1615</v>
+        <v>1738</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1210</v>
+        <v>1087</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1372</v>
+        <v>1418</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1195</v>
+        <v>1151</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>484</v>
+        <v>228</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -838,22 +838,22 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1277</v>
+        <v>1616</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1552</v>
+        <v>1210</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1274</v>
+        <v>1366</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1291</v>
+        <v>1197</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>307</v>
+        <v>487</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -866,22 +866,22 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1115</v>
+        <v>1272</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1708</v>
+        <v>1549</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1231</v>
+        <v>1268</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1330</v>
+        <v>1291</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>127</v>
+        <v>305</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>207</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -894,22 +894,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1186</v>
+        <v>1113</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1632</v>
+        <v>1710</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1251</v>
+        <v>1229</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1304</v>
+        <v>1332</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>275</v>
+        <v>124</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>118</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">
@@ -922,22 +922,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>980</v>
+        <v>1193</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1842</v>
+        <v>1629</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1194</v>
+        <v>1251</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1365</v>
+        <v>1304</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>285</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17">
@@ -950,22 +950,22 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1155</v>
+        <v>977</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1656</v>
+        <v>1837</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1243</v>
+        <v>1193</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1311</v>
+        <v>1360</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>349</v>
+        <v>136</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>120</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18">
@@ -978,106 +978,106 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>884</v>
+        <v>1160</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1928</v>
+        <v>1658</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1182</v>
+        <v>1245</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1373</v>
+        <v>1312</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>191</v>
+        <v>351</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1924</v>
+        <v>1931</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1191</v>
+        <v>1180</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1357</v>
+        <v>1372</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>207</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1094</v>
+        <v>887</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1717</v>
+        <v>1924</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1226</v>
+        <v>1190</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1321</v>
+        <v>1355</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>277</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1398</v>
+        <v>1094</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1417</v>
+        <v>1717</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1307</v>
+        <v>1227</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1235</v>
+        <v>1320</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>211</v>
+        <v>138</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>104</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1634</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>1338</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>1495</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>1379</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>1198</v>
+        <v>1241</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>157</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1420</v>
+        <v>1336</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1411</v>
+        <v>1497</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1401</v>
+        <v>1380</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1178</v>
+        <v>1193</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>230</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1473</v>
+        <v>1418</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1360</v>
+        <v>1413</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1396</v>
+        <v>1401</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>209</v>
+        <v>263</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1553</v>
+        <v>1475</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1279</v>
+        <v>1362</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1414</v>
+        <v>1395</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1164</v>
+        <v>1184</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1541</v>
+        <v>1551</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1295</v>
+        <v>1285</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1402</v>
+        <v>1413</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>247</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1608</v>
+        <v>1544</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1223</v>
+        <v>1289</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1430</v>
+        <v>1399</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1142</v>
+        <v>1173</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>197</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1662</v>
+        <v>1610</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1162</v>
+        <v>1224</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1446</v>
+        <v>1432</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1128</v>
+        <v>1142</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1717</v>
+        <v>1663</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1112</v>
+        <v>1161</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>1447</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>189</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1738</v>
+        <v>1716</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1094</v>
+        <v>1116</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1435</v>
+        <v>1447</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>163</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1738</v>
+        <v>1729</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1418</v>
+        <v>1434</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1151</v>
+        <v>1130</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>278</v>
+        <v>227</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>119</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1616</v>
+        <v>1739</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1206</v>
+        <v>1083</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1370</v>
+        <v>1416</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>228</v>
+        <v>277</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1366</v>
+        <v>1373</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>487</v>
+        <v>233</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1272</v>
+        <v>1616</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1549</v>
+        <v>1210</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1268</v>
+        <v>1363</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1291</v>
+        <v>1203</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>305</v>
+        <v>488</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1113</v>
+        <v>1275</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1710</v>
+        <v>1551</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1229</v>
+        <v>1272</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1332</v>
+        <v>1293</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>124</v>
+        <v>304</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>207</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1193</v>
+        <v>1119</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1629</v>
+        <v>1706</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1251</v>
+        <v>1232</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1304</v>
+        <v>1332</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>274</v>
+        <v>123</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>118</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>977</v>
+        <v>1196</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1837</v>
+        <v>1625</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1193</v>
+        <v>1256</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1360</v>
+        <v>1302</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>282</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1160</v>
+        <v>982</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1658</v>
+        <v>1838</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1245</v>
+        <v>1195</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1312</v>
+        <v>1361</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>351</v>
+        <v>138</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>119</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>882</v>
+        <v>1152</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1931</v>
+        <v>1659</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1180</v>
+        <v>1246</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1372</v>
+        <v>1308</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>188</v>
+        <v>349</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1924</v>
+        <v>1929</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1190</v>
+        <v>1179</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1355</v>
+        <v>1373</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>207</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1094</v>
+        <v>893</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1717</v>
+        <v>1924</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1227</v>
+        <v>1194</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1320</v>
+        <v>1357</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>281</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,343 +523,343 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1209</v>
+        <v>1313</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1634</v>
+        <v>1522</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1338</v>
+        <v>1394</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1241</v>
+        <v>1180</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>192</v>
+        <v>299</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>196</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1336</v>
+        <v>1204</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1497</v>
+        <v>1630</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1380</v>
+        <v>1337</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1193</v>
+        <v>1236</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>149</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1418</v>
+        <v>1335</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1413</v>
+        <v>1498</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1401</v>
+        <v>1380</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>228</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1475</v>
+        <v>1421</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1362</v>
+        <v>1410</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1184</v>
+        <v>1175</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>208</v>
+        <v>266</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1551</v>
+        <v>1466</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1285</v>
+        <v>1362</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1413</v>
+        <v>1394</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1163</v>
+        <v>1179</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>269</v>
+        <v>208</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1289</v>
+        <v>1277</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1399</v>
+        <v>1412</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1173</v>
+        <v>1160</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>197</v>
+        <v>267</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>252</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1610</v>
+        <v>1538</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1224</v>
+        <v>1289</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1432</v>
+        <v>1399</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1142</v>
+        <v>1173</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>194</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1663</v>
+        <v>1605</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1161</v>
+        <v>1220</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1447</v>
+        <v>1431</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1127</v>
+        <v>1141</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>229</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1716</v>
+        <v>1661</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1116</v>
+        <v>1163</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>211</v>
+        <v>268</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>189</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1729</v>
+        <v>1708</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>163</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1739</v>
+        <v>1730</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1083</v>
+        <v>1093</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1416</v>
+        <v>1435</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1150</v>
+        <v>1129</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1620</v>
+        <v>1738</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1207</v>
+        <v>1084</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1373</v>
+        <v>1416</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1191</v>
+        <v>1147</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -869,215 +869,215 @@
         <v>1616</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1203</v>
+        <v>1194</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>488</v>
+        <v>232</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1275</v>
+        <v>1609</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1551</v>
+        <v>1212</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1272</v>
+        <v>1361</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1293</v>
+        <v>1199</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>304</v>
+        <v>484</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1119</v>
+        <v>1268</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1706</v>
+        <v>1553</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1232</v>
+        <v>1269</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1332</v>
+        <v>1290</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>123</v>
+        <v>303</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>210</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1196</v>
+        <v>1117</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1625</v>
+        <v>1702</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1256</v>
+        <v>1231</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1302</v>
+        <v>1327</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>277</v>
+        <v>125</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>117</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>982</v>
+        <v>1190</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1838</v>
+        <v>1625</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1195</v>
+        <v>1252</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1361</v>
+        <v>1303</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>138</v>
+        <v>279</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>282</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1152</v>
+        <v>974</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1659</v>
+        <v>1840</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1246</v>
+        <v>1193</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1308</v>
+        <v>1360</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>349</v>
+        <v>134</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>119</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>888</v>
+        <v>1151</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1929</v>
+        <v>1660</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1179</v>
+        <v>1242</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1373</v>
+        <v>1309</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>191</v>
+        <v>352</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>893</v>
+        <v>883</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1924</v>
+        <v>1928</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1194</v>
+        <v>1180</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1357</v>
+        <v>1369</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>211</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1313</v>
+        <v>1330</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1522</v>
+        <v>1506</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1394</v>
+        <v>1416</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1180</v>
+        <v>1158</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1204</v>
+        <v>1311</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1630</v>
+        <v>1524</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1337</v>
+        <v>1395</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1236</v>
+        <v>1179</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>190</v>
+        <v>331</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>194</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1335</v>
+        <v>1202</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1498</v>
+        <v>1632</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1380</v>
+        <v>1337</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1193</v>
+        <v>1236</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>148</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1421</v>
+        <v>1338</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1410</v>
+        <v>1495</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1398</v>
+        <v>1379</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1175</v>
+        <v>1194</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>226</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1466</v>
+        <v>1419</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1362</v>
+        <v>1412</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1394</v>
+        <v>1399</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1550</v>
+        <v>1467</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1277</v>
+        <v>1361</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1412</v>
+        <v>1393</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>267</v>
+        <v>205</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>196</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1538</v>
+        <v>1551</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1399</v>
+        <v>1412</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1173</v>
+        <v>1160</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1605</v>
+        <v>1540</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1220</v>
+        <v>1287</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1431</v>
+        <v>1400</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1141</v>
+        <v>1172</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>193</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1661</v>
+        <v>1603</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1163</v>
+        <v>1222</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1444</v>
+        <v>1431</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1127</v>
+        <v>1141</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>226</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1708</v>
+        <v>1659</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1115</v>
+        <v>1165</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>1443</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>189</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1730</v>
+        <v>1708</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1093</v>
+        <v>1115</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1738</v>
+        <v>1729</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1416</v>
+        <v>1435</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1147</v>
+        <v>1129</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>282</v>
+        <v>230</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>116</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1616</v>
+        <v>1738</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1206</v>
+        <v>1084</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1367</v>
+        <v>1413</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1609</v>
+        <v>1614</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1361</v>
+        <v>1368</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>484</v>
+        <v>230</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>103</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1268</v>
+        <v>1608</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1553</v>
+        <v>1213</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1269</v>
+        <v>1361</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1290</v>
+        <v>1199</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>303</v>
+        <v>483</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1117</v>
+        <v>1272</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1702</v>
+        <v>1549</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1231</v>
+        <v>1271</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1327</v>
+        <v>1288</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>125</v>
+        <v>305</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>209</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1190</v>
+        <v>1118</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1625</v>
+        <v>1701</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1252</v>
+        <v>1230</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1303</v>
+        <v>1328</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>279</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>114</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>974</v>
+        <v>1187</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1840</v>
+        <v>1628</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1193</v>
+        <v>1253</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1360</v>
+        <v>1302</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>134</v>
+        <v>277</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>281</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1151</v>
+        <v>973</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1660</v>
+        <v>1841</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1242</v>
+        <v>1192</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1309</v>
+        <v>1361</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>352</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>121</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>883</v>
+        <v>1153</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1928</v>
+        <v>1658</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1180</v>
+        <v>1243</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1369</v>
+        <v>1308</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>190</v>
+        <v>350</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1330</v>
+        <v>1271</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1506</v>
+        <v>1568</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>121</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1311</v>
+        <v>1328</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1524</v>
+        <v>1508</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1395</v>
+        <v>1416</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1179</v>
+        <v>1158</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1202</v>
+        <v>1310</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1632</v>
+        <v>1525</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1337</v>
+        <v>1395</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1236</v>
+        <v>1179</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>207</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1338</v>
+        <v>1202</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1495</v>
+        <v>1632</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1379</v>
+        <v>1337</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1194</v>
+        <v>1236</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>148</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1419</v>
+        <v>1338</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1412</v>
+        <v>1495</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1399</v>
+        <v>1379</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1174</v>
+        <v>1194</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>224</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1467</v>
+        <v>1421</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1361</v>
+        <v>1410</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1551</v>
+        <v>1468</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1276</v>
+        <v>1360</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1412</v>
+        <v>1393</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1540</v>
+        <v>1551</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1287</v>
+        <v>1276</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1172</v>
+        <v>1160</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>249</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1603</v>
+        <v>1539</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1222</v>
+        <v>1288</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1431</v>
+        <v>1400</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1141</v>
+        <v>1172</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>191</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1659</v>
+        <v>1603</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1165</v>
+        <v>1222</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>227</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1708</v>
+        <v>1658</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1115</v>
+        <v>1166</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>208</v>
+        <v>266</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>191</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1729</v>
+        <v>1708</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>160</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1738</v>
+        <v>1729</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1413</v>
+        <v>1434</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1614</v>
+        <v>1738</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1208</v>
+        <v>1084</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1368</v>
+        <v>1414</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1193</v>
+        <v>1149</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>483</v>
+        <v>230</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1272</v>
+        <v>1611</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1549</v>
+        <v>1210</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1271</v>
+        <v>1362</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1288</v>
+        <v>1198</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>305</v>
+        <v>484</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1118</v>
+        <v>1271</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1701</v>
+        <v>1550</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1230</v>
+        <v>1271</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1328</v>
+        <v>1288</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>127</v>
+        <v>307</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>209</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1187</v>
+        <v>1116</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1628</v>
+        <v>1703</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1253</v>
+        <v>1231</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1302</v>
+        <v>1327</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>277</v>
+        <v>125</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>112</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>973</v>
+        <v>1187</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1841</v>
+        <v>1628</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1192</v>
+        <v>1252</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1361</v>
+        <v>1303</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>283</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1153</v>
+        <v>973</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1658</v>
+        <v>1841</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1243</v>
+        <v>1193</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1308</v>
+        <v>1360</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>350</v>
+        <v>137</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>123</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1411</v>
+        <v>1437</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1163</v>
+        <v>1138</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>275</v>
+        <v>184</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1328</v>
+        <v>1268</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1508</v>
+        <v>1571</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>121</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1310</v>
+        <v>1328</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1525</v>
+        <v>1508</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1179</v>
+        <v>1156</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>329</v>
+        <v>294</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1202</v>
+        <v>1311</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1632</v>
+        <v>1524</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1337</v>
+        <v>1395</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1236</v>
+        <v>1179</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>207</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1338</v>
+        <v>1204</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1495</v>
+        <v>1630</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1379</v>
+        <v>1337</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1194</v>
+        <v>1236</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1421</v>
+        <v>1338</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1410</v>
+        <v>1495</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1399</v>
+        <v>1380</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>224</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1468</v>
+        <v>1421</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1360</v>
+        <v>1410</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1551</v>
+        <v>1468</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1276</v>
+        <v>1360</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1412</v>
+        <v>1393</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1539</v>
+        <v>1552</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1288</v>
+        <v>1275</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>198</v>
+        <v>270</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>249</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1603</v>
+        <v>1538</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1222</v>
+        <v>1289</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1431</v>
+        <v>1400</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1141</v>
+        <v>1172</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>191</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1658</v>
+        <v>1601</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1166</v>
+        <v>1224</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>227</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1708</v>
+        <v>1658</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1115</v>
+        <v>1166</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1444</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>191</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1729</v>
+        <v>1708</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>162</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1738</v>
+        <v>1729</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1084</v>
+        <v>1094</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1414</v>
+        <v>1433</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1149</v>
+        <v>1131</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1613</v>
+        <v>1735</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1209</v>
+        <v>1087</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1367</v>
+        <v>1413</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1611</v>
+        <v>1616</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>484</v>
+        <v>230</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>101</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1271</v>
+        <v>1611</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1550</v>
+        <v>1210</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1271</v>
+        <v>1363</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1288</v>
+        <v>1197</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>307</v>
+        <v>486</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1116</v>
+        <v>1272</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1703</v>
+        <v>1549</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1231</v>
+        <v>1271</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1327</v>
+        <v>1288</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>125</v>
+        <v>306</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>209</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1187</v>
+        <v>1115</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1628</v>
+        <v>1704</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1252</v>
+        <v>1230</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1303</v>
+        <v>1328</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>276</v>
+        <v>123</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>113</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>973</v>
+        <v>1185</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1841</v>
+        <v>1630</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1193</v>
+        <v>1253</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1360</v>
+        <v>1302</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>137</v>
+        <v>281</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>283</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1281</v>
+        <v>1378</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1558</v>
+        <v>1464</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1437</v>
+        <v>1453</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1138</v>
+        <v>1123</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>184</v>
+        <v>297</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1268</v>
+        <v>1279</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1571</v>
+        <v>1560</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1410</v>
+        <v>1437</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1164</v>
+        <v>1138</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>274</v>
+        <v>182</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1328</v>
+        <v>1266</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1508</v>
+        <v>1572</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>118</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1311</v>
+        <v>1328</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1524</v>
+        <v>1508</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1179</v>
+        <v>1156</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1204</v>
+        <v>1313</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1630</v>
+        <v>1522</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1337</v>
+        <v>1394</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1236</v>
+        <v>1180</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>212</v>
+        <v>331</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>205</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1630</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>1338</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>1495</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1380</v>
-      </c>
       <c r="F7" s="5" t="n">
-        <v>1193</v>
+        <v>1235</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>146</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1421</v>
+        <v>1339</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1410</v>
+        <v>1494</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1398</v>
+        <v>1379</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1175</v>
+        <v>1194</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>228</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1468</v>
+        <v>1420</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1360</v>
+        <v>1411</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1552</v>
+        <v>1469</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1275</v>
+        <v>1359</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1413</v>
+        <v>1394</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1159</v>
+        <v>1179</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>270</v>
+        <v>206</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1289</v>
+        <v>1275</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>198</v>
+        <v>270</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>247</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1601</v>
+        <v>1536</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1224</v>
+        <v>1291</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1429</v>
+        <v>1399</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1143</v>
+        <v>1173</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>192</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1658</v>
+        <v>1601</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1166</v>
+        <v>1224</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1444</v>
+        <v>1430</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1127</v>
+        <v>1142</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>229</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1708</v>
+        <v>1658</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1115</v>
+        <v>1166</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>1443</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>188</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1729</v>
+        <v>1708</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1433</v>
+        <v>1442</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>163</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1735</v>
+        <v>1726</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1087</v>
+        <v>1097</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1413</v>
+        <v>1432</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1150</v>
+        <v>1132</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>124</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1616</v>
+        <v>1739</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1206</v>
+        <v>1083</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1369</v>
+        <v>1415</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1192</v>
+        <v>1148</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1611</v>
+        <v>1616</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>486</v>
+        <v>233</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1272</v>
+        <v>1610</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1549</v>
+        <v>1211</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1271</v>
+        <v>1363</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1288</v>
+        <v>1197</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>306</v>
+        <v>485</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1115</v>
+        <v>1271</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1704</v>
+        <v>1550</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1230</v>
+        <v>1270</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1328</v>
+        <v>1289</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>123</v>
+        <v>304</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>207</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1185</v>
+        <v>1114</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1630</v>
+        <v>1705</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1253</v>
+        <v>1231</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1302</v>
+        <v>1327</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>281</v>
+        <v>128</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>114</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1464</v>
+        <v>1589</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1453</v>
+        <v>1432</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1123</v>
+        <v>1146</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>297</v>
+        <v>162</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>116</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1279</v>
+        <v>1377</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1560</v>
+        <v>1465</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1138</v>
+        <v>1124</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>184</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1266</v>
+        <v>1277</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1572</v>
+        <v>1562</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1411</v>
+        <v>1437</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1163</v>
+        <v>1138</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>275</v>
+        <v>182</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>196</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1328</v>
+        <v>1269</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1508</v>
+        <v>1569</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1313</v>
+        <v>1329</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1522</v>
+        <v>1507</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1394</v>
+        <v>1417</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1180</v>
+        <v>1157</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1630</v>
+        <v>1523</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1338</v>
+        <v>1395</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1235</v>
+        <v>1179</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>213</v>
+        <v>333</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>203</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1339</v>
+        <v>1206</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1494</v>
+        <v>1628</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1379</v>
+        <v>1337</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1194</v>
+        <v>1236</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>149</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1420</v>
+        <v>1337</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1411</v>
+        <v>1496</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1398</v>
+        <v>1379</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1175</v>
+        <v>1194</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>226</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1469</v>
+        <v>1424</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1359</v>
+        <v>1407</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>206</v>
+        <v>266</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1552</v>
+        <v>1468</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1275</v>
+        <v>1360</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1413</v>
+        <v>1394</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1159</v>
+        <v>1179</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>192</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1536</v>
+        <v>1549</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1291</v>
+        <v>1278</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1399</v>
+        <v>1412</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1173</v>
+        <v>1160</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>196</v>
+        <v>267</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>248</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1601</v>
+        <v>1536</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1224</v>
+        <v>1291</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1430</v>
+        <v>1400</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1142</v>
+        <v>1172</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>193</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1658</v>
+        <v>1601</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1166</v>
+        <v>1224</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>227</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1708</v>
+        <v>1658</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1115</v>
+        <v>1166</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>1442</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1726</v>
+        <v>1704</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1097</v>
+        <v>1119</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1739</v>
+        <v>1730</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1083</v>
+        <v>1093</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1415</v>
+        <v>1434</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1148</v>
+        <v>1130</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>281</v>
+        <v>228</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>122</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1616</v>
+        <v>1740</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1206</v>
+        <v>1082</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1370</v>
+        <v>1416</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1191</v>
+        <v>1147</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>233</v>
+        <v>286</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>485</v>
+        <v>230</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>101</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1271</v>
+        <v>1610</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1550</v>
+        <v>1211</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1270</v>
+        <v>1362</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1289</v>
+        <v>1198</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>304</v>
+        <v>483</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1114</v>
+        <v>1270</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1705</v>
+        <v>1551</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1231</v>
+        <v>1271</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1327</v>
+        <v>1288</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>208</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -530,22 +530,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1255</v>
+        <v>1302</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1589</v>
+        <v>1542</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1432</v>
+        <v>1451</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>162</v>
+        <v>313</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -558,22 +558,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1377</v>
+        <v>1254</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1465</v>
+        <v>1590</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1452</v>
+        <v>1432</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1124</v>
+        <v>1146</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>295</v>
+        <v>159</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>119</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
@@ -586,22 +586,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1277</v>
+        <v>1376</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1562</v>
+        <v>1466</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1437</v>
+        <v>1453</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1138</v>
+        <v>1123</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>182</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5">
@@ -614,22 +614,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1412</v>
+        <v>1437</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1162</v>
+        <v>1138</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6">
@@ -642,22 +642,22 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1329</v>
+        <v>1272</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1507</v>
+        <v>1566</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1417</v>
+        <v>1411</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>118</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
@@ -670,22 +670,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1312</v>
+        <v>1328</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1523</v>
+        <v>1508</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1179</v>
+        <v>1156</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>333</v>
+        <v>295</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
@@ -698,22 +698,22 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1206</v>
+        <v>1314</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1628</v>
+        <v>1521</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1337</v>
+        <v>1394</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1236</v>
+        <v>1180</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>207</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9">
@@ -726,22 +726,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1629</v>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>1337</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>1496</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1379</v>
-      </c>
       <c r="F9" s="5" t="n">
-        <v>1194</v>
+        <v>1236</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -754,22 +754,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1424</v>
+        <v>1339</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1407</v>
+        <v>1494</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1400</v>
+        <v>1380</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1173</v>
+        <v>1193</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>226</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -782,22 +782,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1468</v>
+        <v>1423</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1360</v>
+        <v>1408</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>207</v>
+        <v>265</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12">
@@ -810,22 +810,22 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1549</v>
+        <v>1466</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1278</v>
+        <v>1362</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1412</v>
+        <v>1393</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>267</v>
+        <v>205</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>193</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
@@ -838,22 +838,22 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1536</v>
+        <v>1548</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1291</v>
+        <v>1279</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14">
@@ -866,22 +866,22 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1601</v>
+        <v>1535</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1224</v>
+        <v>1292</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1429</v>
+        <v>1399</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1143</v>
+        <v>1173</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>191</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15">
@@ -894,22 +894,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1658</v>
+        <v>1601</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1166</v>
+        <v>1224</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1442</v>
+        <v>1428</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1129</v>
+        <v>1144</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>228</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
@@ -922,22 +922,22 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1704</v>
+        <v>1655</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1119</v>
+        <v>1169</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>192</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17">
@@ -950,22 +950,22 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1730</v>
+        <v>1708</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1093</v>
+        <v>1115</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1434</v>
+        <v>1442</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18">
@@ -978,22 +978,22 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1740</v>
+        <v>1730</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1416</v>
+        <v>1435</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1147</v>
+        <v>1129</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>286</v>
+        <v>233</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19">
@@ -1006,22 +1006,22 @@
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1613</v>
+        <v>1740</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1209</v>
+        <v>1082</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1370</v>
+        <v>1416</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1191</v>
+        <v>1147</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -1034,22 +1034,22 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>483</v>
+        <v>227</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
@@ -1062,22 +1062,22 @@
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1270</v>
+        <v>1609</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1551</v>
+        <v>1212</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1271</v>
+        <v>1363</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1288</v>
+        <v>1197</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>310</v>
+        <v>489</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1302</v>
+        <v>1197</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1542</v>
+        <v>1647</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1451</v>
+        <v>1409</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1129</v>
+        <v>1171</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>120</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1254</v>
+        <v>1299</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1590</v>
+        <v>1545</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1432</v>
+        <v>1451</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>159</v>
+        <v>311</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>219</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1376</v>
+        <v>1253</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1466</v>
+        <v>1591</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1453</v>
+        <v>1432</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1123</v>
+        <v>1146</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>117</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1277</v>
+        <v>1377</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1561</v>
+        <v>1465</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1437</v>
+        <v>1453</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1138</v>
+        <v>1123</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>183</v>
+        <v>295</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>179</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1411</v>
+        <v>1437</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1163</v>
+        <v>1138</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1328</v>
+        <v>1272</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1508</v>
+        <v>1566</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>117</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1314</v>
+        <v>1330</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1521</v>
+        <v>1506</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1394</v>
+        <v>1418</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1180</v>
+        <v>1156</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1205</v>
+        <v>1313</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1629</v>
+        <v>1522</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1337</v>
+        <v>1394</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1236</v>
+        <v>1180</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>210</v>
+        <v>331</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>204</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1339</v>
+        <v>1204</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1494</v>
+        <v>1630</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1380</v>
+        <v>1337</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1193</v>
+        <v>1236</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1423</v>
+        <v>1340</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1408</v>
+        <v>1493</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1400</v>
+        <v>1380</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1173</v>
+        <v>1193</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>226</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1466</v>
+        <v>1421</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1362</v>
+        <v>1410</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1393</v>
+        <v>1400</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1548</v>
+        <v>1464</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1279</v>
+        <v>1364</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1413</v>
+        <v>1393</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1159</v>
+        <v>1180</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>265</v>
+        <v>205</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1535</v>
+        <v>1548</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1292</v>
+        <v>1279</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1399</v>
+        <v>1412</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1173</v>
+        <v>1160</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>246</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1601</v>
+        <v>1536</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1224</v>
+        <v>1291</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1428</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1144</v>
+        <v>1172</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1655</v>
+        <v>1600</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1169</v>
+        <v>1225</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1441</v>
+        <v>1427</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1130</v>
+        <v>1145</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1708</v>
+        <v>1658</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1115</v>
+        <v>1166</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>1442</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>209</v>
+        <v>267</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>191</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1730</v>
+        <v>1707</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1093</v>
+        <v>1116</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>162</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1740</v>
+        <v>1729</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1416</v>
+        <v>1436</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1147</v>
+        <v>1128</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>285</v>
+        <v>233</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1612</v>
+        <v>1739</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1210</v>
+        <v>1083</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1369</v>
+        <v>1415</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1192</v>
+        <v>1148</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>489</v>
+        <v>228</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1197</v>
+        <v>1001</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1647</v>
+        <v>1847</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1409</v>
+        <v>1370</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1171</v>
+        <v>1212</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>328</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1299</v>
+        <v>1197</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1545</v>
+        <v>1647</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1451</v>
+        <v>1409</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1129</v>
+        <v>1171</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>311</v>
+        <v>253</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>118</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1253</v>
+        <v>1299</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1591</v>
+        <v>1545</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1432</v>
+        <v>1451</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>157</v>
+        <v>309</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>219</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1377</v>
+        <v>1253</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1465</v>
+        <v>1591</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1453</v>
+        <v>1433</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1123</v>
+        <v>1145</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>119</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1277</v>
+        <v>1377</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1561</v>
+        <v>1465</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1437</v>
+        <v>1453</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1138</v>
+        <v>1123</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>178</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1566</v>
+        <v>1558</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1411</v>
+        <v>1436</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1163</v>
+        <v>1139</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>191</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1330</v>
+        <v>1271</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1506</v>
+        <v>1567</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>116</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1313</v>
+        <v>1330</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1522</v>
+        <v>1506</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1394</v>
+        <v>1417</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1180</v>
+        <v>1157</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>331</v>
+        <v>293</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1204</v>
+        <v>1311</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1630</v>
+        <v>1524</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1337</v>
+        <v>1394</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1236</v>
+        <v>1180</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>209</v>
+        <v>331</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>204</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1340</v>
+        <v>1208</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1493</v>
+        <v>1626</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1380</v>
+        <v>1338</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1193</v>
+        <v>1235</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>146</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1421</v>
+        <v>1338</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1410</v>
+        <v>1495</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1400</v>
+        <v>1380</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1173</v>
+        <v>1193</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>226</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1464</v>
+        <v>1419</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1364</v>
+        <v>1412</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>205</v>
+        <v>263</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1548</v>
+        <v>1465</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1279</v>
+        <v>1363</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1412</v>
+        <v>1393</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>196</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1536</v>
+        <v>1548</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1291</v>
+        <v>1279</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>245</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1600</v>
+        <v>1535</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1225</v>
+        <v>1292</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1427</v>
+        <v>1397</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1145</v>
+        <v>1175</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>193</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1658</v>
+        <v>1601</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1166</v>
+        <v>1224</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1442</v>
+        <v>1428</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1129</v>
+        <v>1144</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>267</v>
+        <v>233</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>232</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1707</v>
+        <v>1658</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1116</v>
+        <v>1166</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1729</v>
+        <v>1707</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1094</v>
+        <v>1116</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1436</v>
+        <v>1444</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1739</v>
+        <v>1729</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1415</v>
+        <v>1434</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1148</v>
+        <v>1130</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1612</v>
+        <v>1738</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1210</v>
+        <v>1084</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1370</v>
+        <v>1416</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1191</v>
+        <v>1147</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>228</v>
+        <v>282</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1001</v>
+        <v>945</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1847</v>
+        <v>1907</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1370</v>
+        <v>1331</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1212</v>
+        <v>1254</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>283</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1197</v>
+        <v>1002</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1647</v>
+        <v>1846</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1409</v>
+        <v>1370</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1171</v>
+        <v>1212</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>253</v>
+        <v>183</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>326</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1299</v>
+        <v>1196</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1545</v>
+        <v>1648</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1451</v>
+        <v>1409</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1129</v>
+        <v>1171</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>309</v>
+        <v>252</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>122</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1253</v>
+        <v>1299</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1591</v>
+        <v>1545</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1145</v>
+        <v>1128</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>157</v>
+        <v>309</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>220</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1377</v>
+        <v>1253</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1465</v>
+        <v>1591</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1453</v>
+        <v>1433</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1123</v>
+        <v>1145</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>296</v>
+        <v>158</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>115</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1280</v>
+        <v>1381</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1558</v>
+        <v>1461</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1436</v>
+        <v>1452</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1139</v>
+        <v>1124</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>187</v>
+        <v>300</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>176</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1567</v>
+        <v>1559</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1412</v>
+        <v>1437</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1162</v>
+        <v>1138</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>275</v>
+        <v>185</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>189</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1330</v>
+        <v>1271</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1506</v>
+        <v>1567</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1417</v>
+        <v>1411</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>118</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1311</v>
+        <v>1328</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1524</v>
+        <v>1508</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1394</v>
+        <v>1417</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1180</v>
+        <v>1157</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>331</v>
+        <v>292</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1208</v>
+        <v>1314</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1626</v>
+        <v>1521</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1338</v>
+        <v>1395</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1235</v>
+        <v>1179</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>211</v>
+        <v>333</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>202</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>1207</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1627</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>1338</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>1495</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>1380</v>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>1193</v>
+        <v>1235</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>146</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1419</v>
+        <v>1336</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1412</v>
+        <v>1497</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1399</v>
+        <v>1380</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>227</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1465</v>
+        <v>1420</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1363</v>
+        <v>1411</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1548</v>
+        <v>1464</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1279</v>
+        <v>1364</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1413</v>
+        <v>1394</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1159</v>
+        <v>1179</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1535</v>
+        <v>1546</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1292</v>
+        <v>1281</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1397</v>
+        <v>1409</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1601</v>
+        <v>1536</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1224</v>
+        <v>1291</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1428</v>
+        <v>1398</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1144</v>
+        <v>1174</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>194</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1658</v>
+        <v>1600</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1166</v>
+        <v>1225</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>267</v>
+        <v>233</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>230</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1707</v>
+        <v>1659</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1116</v>
+        <v>1165</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>191</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1729</v>
+        <v>1707</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1094</v>
+        <v>1116</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1738</v>
+        <v>1728</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1416</v>
+        <v>1435</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1147</v>
+        <v>1129</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>945</v>
+        <v>1082</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1907</v>
+        <v>1771</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1331</v>
+        <v>1369</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1254</v>
+        <v>1218</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>196</v>
+        <v>329</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>196</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1002</v>
+        <v>946</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1846</v>
+        <v>1906</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1370</v>
+        <v>1331</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1212</v>
+        <v>1254</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>280</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1196</v>
+        <v>1001</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1648</v>
+        <v>1847</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1409</v>
+        <v>1370</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1171</v>
+        <v>1212</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>252</v>
+        <v>181</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>332</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1299</v>
+        <v>1196</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1545</v>
+        <v>1648</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1452</v>
+        <v>1410</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1128</v>
+        <v>1170</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>123</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1253</v>
+        <v>1299</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1591</v>
+        <v>1545</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1145</v>
+        <v>1128</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>158</v>
+        <v>307</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>216</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1381</v>
+        <v>1258</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1461</v>
+        <v>1586</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1452</v>
+        <v>1432</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1124</v>
+        <v>1146</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>300</v>
+        <v>161</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>113</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1279</v>
+        <v>1380</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1559</v>
+        <v>1462</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1138</v>
+        <v>1124</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>185</v>
+        <v>300</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>174</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1567</v>
+        <v>1558</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1411</v>
+        <v>1437</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1163</v>
+        <v>1138</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1328</v>
+        <v>1268</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1508</v>
+        <v>1570</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1417</v>
+        <v>1411</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>118</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1314</v>
+        <v>1332</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1521</v>
+        <v>1504</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1179</v>
+        <v>1156</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>333</v>
+        <v>294</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1207</v>
+        <v>1313</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1627</v>
+        <v>1522</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1338</v>
+        <v>1395</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1235</v>
+        <v>1179</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>211</v>
+        <v>333</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>203</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1336</v>
+        <v>1204</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1497</v>
+        <v>1630</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1380</v>
+        <v>1337</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1193</v>
+        <v>1236</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1420</v>
+        <v>1338</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1411</v>
+        <v>1495</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1399</v>
+        <v>1380</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>229</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1464</v>
+        <v>1418</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1364</v>
+        <v>1413</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>209</v>
+        <v>267</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1546</v>
+        <v>1463</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1281</v>
+        <v>1365</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1163</v>
+        <v>1182</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1536</v>
+        <v>1547</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1291</v>
+        <v>1280</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1174</v>
+        <v>1162</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>249</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1600</v>
+        <v>1536</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1225</v>
+        <v>1291</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1429</v>
+        <v>1399</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1143</v>
+        <v>1173</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>192</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1659</v>
+        <v>1600</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1126</v>
+        <v>1141</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>231</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1707</v>
+        <v>1659</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1116</v>
+        <v>1165</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>1443</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>188</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1728</v>
+        <v>1707</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>164</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1082</v>
+        <v>1159</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1771</v>
+        <v>1694</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1369</v>
+        <v>1389</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1218</v>
+        <v>1199</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>946</v>
+        <v>1083</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1906</v>
+        <v>1770</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1331</v>
+        <v>1369</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1254</v>
+        <v>1218</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>194</v>
+        <v>327</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>193</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1001</v>
+        <v>946</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1847</v>
+        <v>1906</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1370</v>
+        <v>1332</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1212</v>
+        <v>1253</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>287</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1196</v>
+        <v>1001</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1648</v>
+        <v>1847</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1410</v>
+        <v>1371</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1170</v>
+        <v>1211</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>329</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1299</v>
+        <v>1196</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1545</v>
+        <v>1648</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1452</v>
+        <v>1410</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1128</v>
+        <v>1170</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>307</v>
+        <v>254</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>122</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1258</v>
+        <v>1304</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1586</v>
+        <v>1540</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1432</v>
+        <v>1451</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>161</v>
+        <v>309</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1380</v>
+        <v>1255</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1462</v>
+        <v>1589</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1452</v>
+        <v>1431</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1124</v>
+        <v>1147</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>300</v>
+        <v>162</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>112</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1280</v>
+        <v>1381</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1558</v>
+        <v>1461</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1138</v>
+        <v>1124</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>184</v>
+        <v>298</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>175</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1570</v>
+        <v>1560</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1411</v>
+        <v>1437</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1163</v>
+        <v>1138</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>273</v>
+        <v>184</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1332</v>
+        <v>1271</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1504</v>
+        <v>1567</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>118</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1313</v>
+        <v>1331</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1522</v>
+        <v>1505</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1179</v>
+        <v>1156</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>333</v>
+        <v>295</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1204</v>
+        <v>1310</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1630</v>
+        <v>1525</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1337</v>
+        <v>1394</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1236</v>
+        <v>1180</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>208</v>
+        <v>329</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>204</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1338</v>
+        <v>1205</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1495</v>
+        <v>1629</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1380</v>
+        <v>1337</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1193</v>
+        <v>1236</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>150</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1418</v>
+        <v>1338</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1413</v>
+        <v>1495</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1400</v>
+        <v>1382</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1173</v>
+        <v>1191</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>224</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1463</v>
+        <v>1417</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1365</v>
+        <v>1414</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>206</v>
+        <v>264</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1547</v>
+        <v>1464</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1280</v>
+        <v>1364</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1162</v>
+        <v>1181</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>195</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1536</v>
+        <v>1547</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1291</v>
+        <v>1280</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1173</v>
+        <v>1161</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>199</v>
+        <v>268</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>247</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1600</v>
+        <v>1536</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1225</v>
+        <v>1291</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1431</v>
+        <v>1401</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1141</v>
+        <v>1171</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>193</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1659</v>
+        <v>1600</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>229</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1707</v>
+        <v>1657</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1116</v>
+        <v>1167</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>190</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1159</v>
+        <v>1090</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1694</v>
+        <v>1763</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1389</v>
+        <v>1353</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1199</v>
+        <v>1237</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>131</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1083</v>
+        <v>1157</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1770</v>
+        <v>1696</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1369</v>
+        <v>1389</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1218</v>
+        <v>1199</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>946</v>
+        <v>1082</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1906</v>
+        <v>1771</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1332</v>
+        <v>1369</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1253</v>
+        <v>1218</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>191</v>
+        <v>325</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>198</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1001</v>
+        <v>946</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1847</v>
+        <v>1906</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1371</v>
+        <v>1332</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1211</v>
+        <v>1253</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>284</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1196</v>
+        <v>1001</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1648</v>
+        <v>1847</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1410</v>
+        <v>1371</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1170</v>
+        <v>1211</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>327</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1304</v>
+        <v>1199</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1540</v>
+        <v>1645</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1451</v>
+        <v>1410</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1129</v>
+        <v>1170</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>121</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1255</v>
+        <v>1304</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1589</v>
+        <v>1540</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1431</v>
+        <v>1450</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1147</v>
+        <v>1130</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>162</v>
+        <v>308</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>210</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1381</v>
+        <v>1257</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1461</v>
+        <v>1587</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1452</v>
+        <v>1432</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1124</v>
+        <v>1146</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>114</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1278</v>
+        <v>1380</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1560</v>
+        <v>1462</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1138</v>
+        <v>1124</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>184</v>
+        <v>299</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>173</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1412</v>
+        <v>1437</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1162</v>
+        <v>1138</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>275</v>
+        <v>184</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1331</v>
+        <v>1272</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1505</v>
+        <v>1566</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>118</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1310</v>
+        <v>1329</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1525</v>
+        <v>1507</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1394</v>
+        <v>1418</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1180</v>
+        <v>1156</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1205</v>
+        <v>1311</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1629</v>
+        <v>1524</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1337</v>
+        <v>1393</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1236</v>
+        <v>1181</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>208</v>
+        <v>328</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>207</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1629</v>
+      </c>
+      <c r="E15" s="5" t="n">
         <v>1338</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>1495</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>1382</v>
-      </c>
       <c r="F15" s="5" t="n">
-        <v>1191</v>
+        <v>1235</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>145</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1417</v>
+        <v>1336</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1414</v>
+        <v>1497</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1397</v>
+        <v>1381</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1176</v>
+        <v>1192</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>227</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1464</v>
+        <v>1420</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1364</v>
+        <v>1411</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>207</v>
+        <v>265</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1547</v>
+        <v>1463</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1280</v>
+        <v>1365</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1411</v>
+        <v>1392</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1161</v>
+        <v>1181</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1536</v>
+        <v>1546</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1291</v>
+        <v>1281</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1401</v>
+        <v>1412</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1171</v>
+        <v>1160</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1600</v>
+        <v>1536</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1225</v>
+        <v>1291</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1429</v>
+        <v>1400</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1143</v>
+        <v>1172</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>190</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1657</v>
+        <v>1600</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1167</v>
+        <v>1225</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>232</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1090</v>
+        <v>1125</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1763</v>
+        <v>1730</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1353</v>
+        <v>1342</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>203</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1157</v>
+        <v>1087</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1696</v>
+        <v>1766</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1389</v>
+        <v>1353</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1199</v>
+        <v>1237</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1082</v>
+        <v>1159</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1771</v>
+        <v>1694</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1369</v>
+        <v>1389</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1218</v>
+        <v>1199</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>946</v>
+        <v>1082</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1906</v>
+        <v>1771</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1332</v>
+        <v>1369</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1253</v>
+        <v>1218</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>192</v>
+        <v>326</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>198</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1001</v>
+        <v>946</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1847</v>
+        <v>1906</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1371</v>
+        <v>1333</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1211</v>
+        <v>1252</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>284</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1199</v>
+        <v>1004</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1645</v>
+        <v>1844</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1410</v>
+        <v>1372</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1170</v>
+        <v>1210</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>254</v>
+        <v>190</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>326</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1304</v>
+        <v>1201</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1540</v>
+        <v>1643</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1450</v>
+        <v>1408</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1130</v>
+        <v>1172</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>308</v>
+        <v>253</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>121</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1257</v>
+        <v>1302</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1587</v>
+        <v>1542</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1432</v>
+        <v>1451</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>162</v>
+        <v>307</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1380</v>
+        <v>1257</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1462</v>
+        <v>1587</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1452</v>
+        <v>1432</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1124</v>
+        <v>1146</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>299</v>
+        <v>162</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>114</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1277</v>
+        <v>1378</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1561</v>
+        <v>1464</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1437</v>
+        <v>1451</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1138</v>
+        <v>1125</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>184</v>
+        <v>298</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>171</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1272</v>
+        <v>1281</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1566</v>
+        <v>1557</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1412</v>
+        <v>1439</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1162</v>
+        <v>1136</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>276</v>
+        <v>188</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1329</v>
+        <v>1269</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1507</v>
+        <v>1569</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>117</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1311</v>
+        <v>1328</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1524</v>
+        <v>1508</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1393</v>
+        <v>1416</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1181</v>
+        <v>1158</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>328</v>
+        <v>291</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1205</v>
+        <v>1312</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1629</v>
+        <v>1523</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1338</v>
+        <v>1395</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1235</v>
+        <v>1179</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>209</v>
+        <v>329</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>205</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1336</v>
+        <v>1203</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1497</v>
+        <v>1631</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1381</v>
+        <v>1337</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1192</v>
+        <v>1236</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>146</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1420</v>
+        <v>1339</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1411</v>
+        <v>1494</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1398</v>
+        <v>1380</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1175</v>
+        <v>1193</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>227</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1463</v>
+        <v>1417</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1365</v>
+        <v>1414</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>209</v>
+        <v>265</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1546</v>
+        <v>1464</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1281</v>
+        <v>1364</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1412</v>
+        <v>1394</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1160</v>
+        <v>1179</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1536</v>
+        <v>1547</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1291</v>
+        <v>1280</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>246</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1600</v>
+        <v>1536</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1225</v>
+        <v>1291</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1429</v>
+        <v>1400</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1143</v>
+        <v>1172</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1125</v>
+        <v>1091</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1730</v>
+        <v>1765</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1342</v>
+        <v>1334</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1250</v>
+        <v>1259</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>167</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1087</v>
+        <v>1122</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1766</v>
+        <v>1733</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1353</v>
+        <v>1342</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>201</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1159</v>
+        <v>1090</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1694</v>
+        <v>1763</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1389</v>
+        <v>1353</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1199</v>
+        <v>1237</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>130</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1082</v>
+        <v>1159</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1771</v>
+        <v>1694</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1369</v>
+        <v>1389</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1218</v>
+        <v>1199</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>946</v>
+        <v>1082</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1906</v>
+        <v>1771</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1333</v>
+        <v>1370</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1252</v>
+        <v>1217</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>192</v>
+        <v>327</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>198</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1004</v>
+        <v>948</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1844</v>
+        <v>1904</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1372</v>
+        <v>1333</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1210</v>
+        <v>1252</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>278</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1201</v>
+        <v>1008</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1643</v>
+        <v>1840</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1408</v>
+        <v>1371</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1172</v>
+        <v>1211</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>253</v>
+        <v>193</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>325</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1302</v>
+        <v>1199</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1542</v>
+        <v>1645</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1451</v>
+        <v>1409</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1129</v>
+        <v>1171</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>121</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1257</v>
+        <v>1300</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1587</v>
+        <v>1544</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1432</v>
+        <v>1450</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1146</v>
+        <v>1130</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>162</v>
+        <v>307</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>209</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1378</v>
+        <v>1257</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1464</v>
+        <v>1587</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1451</v>
+        <v>1432</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1125</v>
+        <v>1146</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>112</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1281</v>
+        <v>1380</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1557</v>
+        <v>1462</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1439</v>
+        <v>1452</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>188</v>
+        <v>302</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>171</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1269</v>
+        <v>1280</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1569</v>
+        <v>1558</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1411</v>
+        <v>1439</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1163</v>
+        <v>1136</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>189</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1328</v>
+        <v>1268</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1508</v>
+        <v>1570</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>123</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1312</v>
+        <v>1328</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1523</v>
+        <v>1508</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1179</v>
+        <v>1156</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>329</v>
+        <v>291</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1203</v>
+        <v>1310</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1631</v>
+        <v>1525</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1337</v>
+        <v>1394</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1236</v>
+        <v>1180</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>203</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1339</v>
+        <v>1206</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1494</v>
+        <v>1628</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1380</v>
+        <v>1336</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1193</v>
+        <v>1237</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1417</v>
+        <v>1335</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1414</v>
+        <v>1498</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1398</v>
+        <v>1380</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1175</v>
+        <v>1193</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>226</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1464</v>
+        <v>1417</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1364</v>
+        <v>1414</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>208</v>
+        <v>264</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1547</v>
+        <v>1465</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1280</v>
+        <v>1363</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1413</v>
+        <v>1394</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1159</v>
+        <v>1179</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1536</v>
+        <v>1547</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1291</v>
+        <v>1280</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1400</v>
+        <v>1413</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1172</v>
+        <v>1159</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>248</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1091</v>
+        <v>1043</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1765</v>
+        <v>1816</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1334</v>
+        <v>1312</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1259</v>
+        <v>1283</v>
       </c>
       <c r="G2" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>213</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1122</v>
+        <v>1087</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1733</v>
+        <v>1769</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1342</v>
+        <v>1334</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1250</v>
+        <v>1259</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>165</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1090</v>
+        <v>1122</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1763</v>
+        <v>1733</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1353</v>
+        <v>1342</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>202</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1159</v>
+        <v>1092</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1694</v>
+        <v>1761</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1389</v>
+        <v>1353</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1199</v>
+        <v>1237</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>134</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1082</v>
+        <v>1157</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1771</v>
+        <v>1696</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1370</v>
+        <v>1390</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1217</v>
+        <v>1198</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>948</v>
+        <v>1084</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1904</v>
+        <v>1769</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1333</v>
+        <v>1370</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1252</v>
+        <v>1217</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>194</v>
+        <v>328</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>193</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1008</v>
+        <v>951</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1840</v>
+        <v>1901</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1371</v>
+        <v>1332</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1211</v>
+        <v>1253</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>278</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1199</v>
+        <v>1007</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1645</v>
+        <v>1841</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1409</v>
+        <v>1372</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1171</v>
+        <v>1210</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>251</v>
+        <v>190</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>327</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1300</v>
+        <v>1198</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1544</v>
+        <v>1646</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1450</v>
+        <v>1407</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1130</v>
+        <v>1173</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>120</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1257</v>
+        <v>1299</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1587</v>
+        <v>1545</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1432</v>
+        <v>1451</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1146</v>
+        <v>1129</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>162</v>
+        <v>307</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>206</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1380</v>
+        <v>1262</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1462</v>
+        <v>1582</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1452</v>
+        <v>1433</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1124</v>
+        <v>1145</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>302</v>
+        <v>165</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>114</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1558</v>
+        <v>1464</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1439</v>
+        <v>1452</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>186</v>
+        <v>301</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>170</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1268</v>
+        <v>1280</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1570</v>
+        <v>1558</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1409</v>
+        <v>1437</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1165</v>
+        <v>1138</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>271</v>
+        <v>181</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1328</v>
+        <v>1266</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1508</v>
+        <v>1572</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>121</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1310</v>
+        <v>1328</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1525</v>
+        <v>1508</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1394</v>
+        <v>1417</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1180</v>
+        <v>1157</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1206</v>
+        <v>1311</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1628</v>
+        <v>1524</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1336</v>
+        <v>1393</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1237</v>
+        <v>1181</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>205</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1335</v>
+        <v>1203</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1498</v>
+        <v>1631</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1380</v>
+        <v>1336</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1193</v>
+        <v>1237</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>148</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1417</v>
+        <v>1333</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1400</v>
+        <v>1382</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1173</v>
+        <v>1191</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>227</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1465</v>
+        <v>1419</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1363</v>
+        <v>1412</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1547</v>
+        <v>1467</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1280</v>
+        <v>1361</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1413</v>
+        <v>1394</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1159</v>
+        <v>1179</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/data/chartink_scan_counts.xlsx
+++ b/data/chartink_scan_counts.xlsx
@@ -523,561 +523,561 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1043</v>
+        <v>930</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1816</v>
+        <v>1931</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1087</v>
+        <v>1040</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1769</v>
+        <v>1819</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1334</v>
+        <v>1312</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1259</v>
+        <v>1283</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>243</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1122</v>
+        <v>1087</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1733</v>
+        <v>1769</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1342</v>
+        <v>1334</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1250</v>
+        <v>1259</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>166</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1092</v>
+        <v>1123</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1761</v>
+        <v>1732</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1353</v>
+        <v>1342</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>206</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1157</v>
+        <v>1092</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1696</v>
+        <v>1761</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1390</v>
+        <v>1354</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1198</v>
+        <v>1236</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>133</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1084</v>
+        <v>1158</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1769</v>
+        <v>1695</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1370</v>
+        <v>1390</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1217</v>
+        <v>1198</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>99</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>951</v>
+        <v>1087</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1901</v>
+        <v>1766</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1332</v>
+        <v>1369</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1253</v>
+        <v>1218</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>199</v>
+        <v>331</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>192</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1007</v>
+        <v>949</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1841</v>
+        <v>1903</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1372</v>
+        <v>1333</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1210</v>
+        <v>1252</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>279</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1198</v>
+        <v>1007</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1646</v>
+        <v>1841</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1407</v>
+        <v>1371</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1173</v>
+        <v>1211</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>251</v>
+        <v>191</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>326</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1299</v>
+        <v>1195</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1545</v>
+        <v>1649</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1451</v>
+        <v>1407</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>307</v>
+        <v>252</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>117</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1262</v>
+        <v>1304</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1582</v>
+        <v>1540</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1145</v>
+        <v>1128</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>165</v>
+        <v>312</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>206</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1378</v>
+        <v>1260</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1464</v>
+        <v>1584</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1452</v>
+        <v>1433</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1124</v>
+        <v>1145</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>115</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1280</v>
+        <v>1378</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1558</v>
+        <v>1464</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1437</v>
+        <v>1450</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>181</v>
+        <v>296</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>174</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1266</v>
+        <v>1279</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1572</v>
+        <v>1559</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1411</v>
+        <v>1439</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1163</v>
+        <v>1136</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>273</v>
+        <v>184</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1328</v>
+        <v>1265</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1508</v>
+        <v>1573</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>119</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1311</v>
+        <v>1329</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1524</v>
+        <v>1507</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1393</v>
+        <v>1416</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1181</v>
+        <v>1158</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>330</v>
+        <v>294</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1203</v>
+        <v>1309</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1631</v>
+        <v>1526</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1336</v>
+        <v>1393</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1237</v>
+        <v>1181</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>210</v>
+        <v>329</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>204</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1333</v>
+        <v>1202</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1500</v>
+        <v>1632</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1382</v>
+        <v>1338</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1191</v>
+        <v>1235</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>151</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1419</v>
+        <v>1335</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1412</v>
+        <v>1498</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1400</v>
+        <v>1382</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1173</v>
+        <v>1191</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>224</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1467</v>
+        <v>1420</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1361</v>
+        <v>1411</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
